--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711188F2-4E49-4151-8493-341A8430CE55}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16FFD9B4-FF49-448D-830F-E6497224357D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
@@ -1863,6 +1863,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4529,10 +4533,10 @@
         <v>29</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>61</v>
@@ -5476,13 +5480,13 @@
           <x14:formula1>
             <xm:f>Information!$A$1:$A$79</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A47 K2:K47 I2:I47 G2:G47 E2:E47 C2:C47</xm:sqref>
+          <xm:sqref>A2:A47 K2:K47 I2:I47 C2:C47 E2:E47 G2:G47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B47 L2:L47 F2:F47 J2:J47 H2:H47 D2:D47</xm:sqref>
+          <xm:sqref>B2:B47 L2:L47 F2:F47 J2:J47 D2:D47 H2:H47</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16FFD9B4-FF49-448D-830F-E6497224357D}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13BD1F2A-E130-43B6-88D9-8B92160CA970}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
+    <workbookView xWindow="9276" yWindow="5136" windowWidth="13764" windowHeight="6384" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" r:id="rId1"/>
@@ -1072,7 +1072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="184">
   <si>
     <t>Animus</t>
   </si>
@@ -1552,6 +1552,78 @@
   </si>
   <si>
     <t xml:space="preserve">Nevette (เร็วสุด) Skill 3 → Kethos Skill 3 ใส่ Tiamat →  XL Skill 3 → Nevette Skill 3 [ลำดับการฆ่า Sania, XC, Tiamat] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kethos (เร็วสุด) Skill 2 (*Sharon no BW) → Fuqiu Skill 3 → Kethos Skill 3 ใส่ Sharon → Ray Skill 3 และหาจังหวะ Execute Sharon [ลำดับการฆ่า Sharon, Kethos, Fiamelia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Areal  (เร็วสุด) Skill 3 ใส่ XL → XC Skill 3 → Sania Skill 3 ให้ Asal → Asal Skill 2  → เน้นจัดการ XL ก่อน → Sania เก็บ Skill 3 ไว้ล้างหลังดีบัฟจาก XC [ลำดับการฆ่า XL, XC, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliam Skill 3 ใส่ Sharon → Gianc Skill 3 ใส่ Sharon → Fuqiu Skill 3 → เน้นจัดการ Sharon ก่อน [ลำดับการฆ่า Sharon, Luvia, Linglua] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kethos (เร็วสุด) Skill 3 ใส่ XL → Lowan Skill 3 ใส่ XL → Kethos Skill 2 → Lowan Skill 2 → เน้นจัดการ XL ก่อน [ลำดับการฆ่า XL, XC, Valerian] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn ตีธรรมดา Nathenn → Sharon Skill 3 → Areal Skill 3 →  Nathenn Skill 3 → Sharon ตีธรรมดา Nathenn → Nathenn หาจังหวะ Execute Raymerry [ลำดับการฆ่า Raymerry, Nathenn, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn (เร็วสุด) Skill 3 →Lowan Skill 3 ใส่ Nathenn →  Areal Skill 3 → Lowan Skill 2 → Nathenn หาจังหวะ Execute Nathenn [ลำดับการฆ่า Nathenn, Kethos, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Ray → Lingluo Skill 3 → Valerian Skill 3 → Asal Skill 2 → Lingluo Skill 2 → เน้นจัดการ Ray ก่อน [ลำดับการฆ่า Raymerry, Gianc, Fiamelia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danvery Skill 3 ใส่ XC → Lowan Skill 3 ใส่ Sharon → Fiamelia Skill 3  → Danvery ตีธรรมดาคอยดึงเกจ XC → Lowan เน้นตี Sharon [ลำดับการฆ่า Sharon, XC, Sylvia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Lowan → Sharon Skill 3 → Fuqiu Skill 3 → Luvia Skill 2 → เน้นจัดการให้ Tiamat เข้า Amber ก่อน แล้วฆ่า Sania + Luvia คอยหุบ Lowan  [ลำดับการฆ่า Sania, Tiamat, Lowan] </t>
+  </si>
+  <si>
+    <t>Doki (เร็วสุด) Skill 3 → XL Skill 3 → Massiah Skill 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Ray → XC ตีธรรมดา XL → Sania ตีธรรมดา XL → Luvia Skill 2 → XC Skill 3 → เน้นจัดการ XL ก่อน + Luvia คอยหุบ Ray [ลำดับการฆ่า XL, Areal, Ray] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kethos Skill 3 ใส่ XL → Fiamelia Skill 3 (หลัง XC Skill 3) → Kethos Skill 2 → Ray Skill 3 หรือหาจังหวะ Execute XL [ลำดับการฆ่า XL, XC, Sylvia] </t>
+  </si>
+  <si>
+    <t>XC Skill 3 → Areal Skill 3  → Nathenn Skill 3 [เน้น Build - Bloodbath]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan Skill 3 ใส่ Kethos →  Areal Skill 3 →  XL Skill 3 → Lowan Skill 2 ใส่ Kethos → เน้นจัดการ Kethos ก่อน จากนั้นค่อยให้ Lowan ค่อย Skill 3 ใส่ Nathenn [ลำดับการฆ่า Kethos, Nathenn, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn (เร็วสุด) Skill 3 → Sylvia Skill 2 ให้ Nathenn →  Ray Skill 3 → Nathenn ตีธรรมดา Sharon → เน้นจัดการ Sharon ก่อน แล้วหาจังหวะ Execute Tiamat [ลำดับการฆ่า Sharon, Tiamat, Fuqiu] </t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset → Buff Piayera → Piayera Skill 3 → Nathenn Skill 3 → Nathenn หาจังหวะ Execute Nathenn [ลำดับการฆ่า Nathenn, Kethos, Sylvia]</t>
+  </si>
+  <si>
+    <t>Piayera (เร็วสุด) Skill 3 + Buff → Sharon Skill 3 → Valerian Skill 3 → เน้นเพิ่ม CD ให้ Sania ฮีลไม่ได้ + ใช้ DOT จาก Sharon ทำ damage [ลำดับการฆ่า Sania, Kethos, Sylvia]</t>
+  </si>
+  <si>
+    <t>Sania Skill 3 ใส่ Tiamat → Ray Skill 3 → Sania ตีธรรมดา Fiamelia → Ray หาจังหวะ Execute [ลำดับการฆ่า Sylvia, Fiamelia, Ray]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn Skill 3 → Lowan Skill 3 ใส่ Areal → Areal Skill 3 → Nathenn ตีธรรมดา Areal → Lowan ตีธรรมดา Areal →  เน้นจัดการ Areal ก่อน แล้วให้ Lowan Skill 3 ใส่ XC โดย Nathenn เก็บ Skill 2 ไว้ Execute [ลำดับการฆ่า Areal, XC, Nathenn] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn Skill 3 → Areal Skill 3 → Ray Skill 3 →  Nathenn ตีธรรมดา Areal → Ray ตีธรรมดา Lowan →  หาจังหวะ Execute Lowan ก่อน [ลำดับการฆ่า Lowan, Tiamate, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danvery (เร็วสุด) Skill 3 ใส่ Lowan → Piayera Skill 3 + ตีธรรมดา Areal → Ray Skill 3  → Danvery ตีธรรมดาคอยดึงเกจ Lowan → Piayera เน้นเพิ่ม CD ใส่ Areal + Ray หาจังหวะ Execute [ลำดับการฆ่า Lowan, Tiamat, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn Skill 3 → Lowan Skill 3 ใส่ XC → Areal Skill 3 →  Nathenn ตีธรรมดา XC → Lowan ตีธรรมดา XC →  หาจังหวะ Execute XC ก่อน [ลำดับการฆ่า XC, Liliam, Valerian] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn Skill 3 → Asal Skill 3 ใส่ Fiamelia → Nathen Skill 2  ใส่ Fiamelia →  Valerian Skill 3 → Nathen ตีธรรมดา Sharon → Asal Skill 2 [ลำดับการฆ่า Fiamelia, Sharon, Raymerry] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Lowan → Areal Skill 3 →  Valerian Skill 3 → Asal Skill 2 → Asal คอยตีเพิ่ม Stack ไปเรื่อยๆ + หาจังหวะปาด [ลำดับการฆ่า Lowan, Tiamat, Areal] **ทีมนี้เล่นยาก ต้องดูจังหวะดีๆ** </t>
   </si>
 </sst>
 </file>
@@ -1776,8 +1848,8 @@
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120081</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>302961</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1824,8 +1896,8 @@
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>394914</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>480060</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2759,10 +2831,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" style="11" customWidth="1"/>
     <col min="3" max="3" width="5.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" style="5" customWidth="1"/>
-    <col min="5" max="6" width="5.77734375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2776,7 +2849,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
@@ -2790,7 +2863,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
@@ -2804,7 +2877,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -2818,7 +2891,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -2832,7 +2905,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
@@ -2846,7 +2919,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -2860,7 +2933,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
@@ -2874,7 +2947,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
@@ -2888,7 +2961,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
@@ -2902,7 +2975,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -2916,7 +2989,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
@@ -2930,7 +3003,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>24</v>
       </c>
@@ -2944,7 +3017,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
@@ -2958,7 +3031,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>28</v>
       </c>
@@ -2972,7 +3045,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>30</v>
       </c>
@@ -2986,7 +3059,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>32</v>
       </c>
@@ -3000,7 +3073,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>34</v>
       </c>
@@ -3014,7 +3087,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>36</v>
       </c>
@@ -3028,7 +3101,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>38</v>
       </c>
@@ -3042,7 +3115,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
@@ -3056,7 +3129,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
@@ -3070,7 +3143,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>44</v>
       </c>
@@ -3084,7 +3157,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>46</v>
       </c>
@@ -3098,7 +3171,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>48</v>
       </c>
@@ -3112,7 +3185,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>50</v>
       </c>
@@ -3120,7 +3193,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>51</v>
       </c>
@@ -3128,7 +3201,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>52</v>
       </c>
@@ -3136,7 +3209,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>53</v>
       </c>
@@ -3144,7 +3217,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>54</v>
       </c>
@@ -3152,7 +3225,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>55</v>
       </c>
@@ -3160,7 +3233,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>56</v>
       </c>
@@ -3168,7 +3241,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>57</v>
       </c>
@@ -3176,7 +3249,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>58</v>
       </c>
@@ -3184,7 +3257,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>59</v>
       </c>
@@ -3192,7 +3265,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>60</v>
       </c>
@@ -3200,7 +3273,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>61</v>
       </c>
@@ -3208,7 +3281,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
@@ -3216,7 +3289,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>63</v>
       </c>
@@ -3224,7 +3297,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>64</v>
       </c>
@@ -3232,7 +3305,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>65</v>
       </c>
@@ -3240,7 +3313,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>66</v>
       </c>
@@ -3248,7 +3321,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>67</v>
       </c>
@@ -3256,7 +3329,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
         <v>68</v>
       </c>
@@ -3264,7 +3337,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>69</v>
       </c>
@@ -3272,7 +3345,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>70</v>
       </c>
@@ -3280,7 +3353,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>71</v>
       </c>
@@ -3288,7 +3361,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>72</v>
       </c>
@@ -3296,7 +3369,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>73</v>
       </c>
@@ -3304,7 +3377,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>74</v>
       </c>
@@ -3312,7 +3385,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>75</v>
       </c>
@@ -3320,7 +3393,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>76</v>
       </c>
@@ -3328,7 +3401,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>77</v>
       </c>
@@ -3336,7 +3409,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>78</v>
       </c>
@@ -3344,7 +3417,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>79</v>
       </c>
@@ -3352,7 +3425,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>80</v>
       </c>
@@ -3360,7 +3433,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>81</v>
       </c>
@@ -3368,7 +3441,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>82</v>
       </c>
@@ -3376,7 +3449,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>83</v>
       </c>
@@ -3384,7 +3457,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>84</v>
       </c>
@@ -3392,7 +3465,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>85</v>
       </c>
@@ -3400,7 +3473,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>86</v>
       </c>
@@ -3408,7 +3481,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>87</v>
       </c>
@@ -3416,7 +3489,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>88</v>
       </c>
@@ -3424,7 +3497,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>89</v>
       </c>
@@ -3432,7 +3505,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>90</v>
       </c>
@@ -3440,7 +3513,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>91</v>
       </c>
@@ -3448,7 +3521,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>92</v>
       </c>
@@ -3456,7 +3529,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>93</v>
       </c>
@@ -3464,7 +3537,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>94</v>
       </c>
@@ -3472,7 +3545,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
         <v>95</v>
       </c>
@@ -3480,7 +3553,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>96</v>
       </c>
@@ -3488,7 +3561,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>97</v>
       </c>
@@ -3496,7 +3569,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>98</v>
       </c>
@@ -3504,7 +3577,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>99</v>
       </c>
@@ -3512,7 +3585,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>100</v>
       </c>
@@ -3520,7 +3593,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>101</v>
       </c>
@@ -3528,7 +3601,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>102</v>
       </c>
@@ -3536,7 +3609,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>103</v>
       </c>
@@ -3552,7 +3625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8DF62-D3A8-45C5-B4BC-03270E337BE8}">
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="18" bestFit="1" customWidth="1"/>
@@ -5271,7 +5344,7 @@
         <v>23</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H42" s="22" t="s">
         <v>35</v>
@@ -5456,20 +5529,1296 @@
         <v>159</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="25"/>
+    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J47" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L47" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M47" s="25" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H48" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J48" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="L48" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H49" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="J49" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K49" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="L49" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M49" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J50" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L50" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" s="25" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J51" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K51" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="L51" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J52" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K52" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L52" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M52" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H53" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J53" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="L53" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M54" s="19" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J55" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K55" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M55" s="25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H56" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J56" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="L56" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="M56" s="25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H57" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J57" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L57" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" s="25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="J58" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A59" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H59" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J59" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K59" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M59" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I60" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J60" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="J61" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K61" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L61" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M61" s="25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="J62" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="L62" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M62" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="J63" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L63" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M63" s="25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A64" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H64" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="J64" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="L64" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M64" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J65" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K65" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L65" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" s="25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J66" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K66" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="L66" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M66" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="J67" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K67" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M67" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A68" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I68" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J68" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L68" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M68" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H69" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J69" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K69" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L69" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J70" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K70" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L70" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M70" s="25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="H71" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="J71" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K71" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="L71" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M71" s="25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="20"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="22"/>
+      <c r="K72" s="23"/>
+      <c r="L72" s="22"/>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A73" s="20"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="22"/>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A74" s="20"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="22"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="22"/>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A75" s="20"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="23"/>
+      <c r="L75" s="22"/>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="20"/>
+      <c r="B76" s="21"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="22"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="22"/>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A77" s="20"/>
+      <c r="B77" s="21"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="21"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="23"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="23"/>
+      <c r="L77" s="22"/>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A78" s="20"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="23"/>
+      <c r="L78" s="22"/>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A79" s="20"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="22"/>
+      <c r="K79" s="23"/>
+      <c r="L79" s="22"/>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A80" s="20"/>
+      <c r="B80" s="21"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="23"/>
+      <c r="L80" s="22"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="20"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="22"/>
+      <c r="K81" s="23"/>
+      <c r="L81" s="22"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="20"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="23"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="23"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="23"/>
+      <c r="L82" s="22"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="20"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="22"/>
+      <c r="K83" s="23"/>
+      <c r="L83" s="22"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="20"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="21"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="23"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="23"/>
+      <c r="L84" s="22"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="20"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="23"/>
+      <c r="J85" s="22"/>
+      <c r="K85" s="23"/>
+      <c r="L85" s="22"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="20"/>
+      <c r="B86" s="21"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="21"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="23"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="23"/>
+      <c r="L86" s="22"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="20"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="20"/>
+      <c r="F87" s="21"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="22"/>
+      <c r="I87" s="23"/>
+      <c r="J87" s="22"/>
+      <c r="K87" s="23"/>
+      <c r="L87" s="22"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="20"/>
+      <c r="B88" s="21"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="21"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="21"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="22"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="22"/>
+      <c r="K88" s="23"/>
+      <c r="L88" s="22"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="20"/>
+      <c r="B89" s="21"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="21"/>
+      <c r="E89" s="20"/>
+      <c r="F89" s="21"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="22"/>
+      <c r="I89" s="23"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="23"/>
+      <c r="L89" s="22"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="20"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="20"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="22"/>
+      <c r="I90" s="23"/>
+      <c r="J90" s="22"/>
+      <c r="K90" s="23"/>
+      <c r="L90" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5480,13 +6829,13 @@
           <x14:formula1>
             <xm:f>Information!$A$1:$A$79</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A47 K2:K47 I2:I47 C2:C47 E2:E47 G2:G47</xm:sqref>
+          <xm:sqref>K2:K90 I2:I90 G2:G90 E2:E90 C2:C90 A2:A90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B47 L2:L47 F2:F47 J2:J47 D2:D47 H2:H47</xm:sqref>
+          <xm:sqref>L2:L90 F2:F90 J2:J90 H2:H90 D2:D90 B2:B90</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13BD1F2A-E130-43B6-88D9-8B92160CA970}"/>
+  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894F8124-E541-4651-85FC-684F3C6207E8}"/>
   <bookViews>
-    <workbookView xWindow="9276" yWindow="5136" windowWidth="13764" windowHeight="6384" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" r:id="rId1"/>
@@ -1072,7 +1072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="185">
   <si>
     <t>Animus</t>
   </si>
@@ -1624,6 +1624,9 @@
   </si>
   <si>
     <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Lowan → Areal Skill 3 →  Valerian Skill 3 → Asal Skill 2 → Asal คอยตีเพิ่ม Stack ไปเรื่อยๆ + หาจังหวะปาด [ลำดับการฆ่า Lowan, Tiamat, Areal] **ทีมนี้เล่นยาก ต้องดูจังหวะดีๆ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharon (เร็วสุด) Skill 3 → Nevette Skill 3 → Heinrich Skill 2 → ทำซ้ำอีกรอบแล้วไล่ฆ่าทีละตัว [ลำดับการฆ่า Viper, Valerian, Asal] **ตัว CC ใช้อะไรก็ได้ เช่น Nevette, Obol** </t>
   </si>
 </sst>
 </file>
@@ -6554,19 +6557,46 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A72" s="20"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="22"/>
-      <c r="K72" s="23"/>
-      <c r="L72" s="22"/>
+    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H72" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="J72" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K72" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M72" s="25" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="20"/>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="564" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894F8124-E541-4651-85FC-684F3C6207E8}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B71B990D-508D-4563-AF9D-24D947B89AC2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
@@ -1072,7 +1072,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="186">
   <si>
     <t>Animus</t>
   </si>
@@ -1627,6 +1627,9 @@
   </si>
   <si>
     <t xml:space="preserve">Sharon (เร็วสุด) Skill 3 → Nevette Skill 3 → Heinrich Skill 2 → ทำซ้ำอีกรอบแล้วไล่ฆ่าทีละตัว [ลำดับการฆ่า Viper, Valerian, Asal] **ตัว CC ใช้อะไรก็ได้ เช่น Nevette, Obol** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathenn (เร็วสุด) Skill 3 → Luvia หุบ Viper →  Areal Skill 3 → Nathenn ตีธรรมดา Asal + หาจังหวะ Execute Asal [ลำดับการฆ่า Asal, Valerian, Viper] </t>
   </si>
 </sst>
 </file>
@@ -6598,19 +6601,46 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A73" s="20"/>
-      <c r="B73" s="21"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="23"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="23"/>
-      <c r="L73" s="22"/>
+    <row r="73" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G73" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H73" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J73" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K73" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="L73" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M73" s="25" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="20"/>
@@ -6859,13 +6889,13 @@
           <x14:formula1>
             <xm:f>Information!$A$1:$A$79</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K90 I2:I90 G2:G90 E2:E90 C2:C90 A2:A90</xm:sqref>
+          <xm:sqref>K2:K90 I2:I90 G2:G90 A2:A90 C2:C90 E2:E90</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L90 F2:F90 J2:J90 H2:H90 D2:D90 B2:B90</xm:sqref>
+          <xm:sqref>L2:L90 J2:J90 H2:H90 B2:B90 D2:D90 F2:F90</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B71B990D-508D-4563-AF9D-24D947B89AC2}"/>
+  <xr:revisionPtr revIDLastSave="1149" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4BD0B21-9AE5-45AD-86C4-A02264C521EE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
+    <workbookView xWindow="-84" yWindow="1116" windowWidth="10320" windowHeight="10524" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="102">
+  <futureMetadata name="XLRICHVALUE" count="103">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -759,8 +759,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="102"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="102">
+  <valueMetadata count="103">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -1066,13 +1073,16 @@
     </bk>
     <bk>
       <rc t="1" v="101"/>
+    </bk>
+    <bk>
+      <rc t="1" v="102"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="217">
   <si>
     <t>Animus</t>
   </si>
@@ -1431,9 +1441,6 @@
     <t>Sylvia (เร็วสุด) Reset → Buff Nathenn → Nathenn Skill 3 → Luvia คอยหุบ Areal → ตี Asal และหาจังหวะ Execute Asal [ลำดับการฆ่า Asal, Nathenn, Areal]</t>
   </si>
   <si>
-    <t>Nathenn (เร็วสุด) ตีธรรมดา → Sylvia Reset → Buff Nathenn → Kethos Skill 2 → หาจังหวะ Execute Nathenn [ลำดับการฆ่า Nathenn, Kethos, Sylvia]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Doki (เร็วสุด) Skill 3 → Liliam Skill 3 ใส่ XC → Ray Skill 3 [ลำดับการฆ่า XC, Sharon, Sylvia] </t>
   </si>
   <si>
@@ -1630,6 +1637,102 @@
   </si>
   <si>
     <t xml:space="preserve">Nathenn (เร็วสุด) Skill 3 → Luvia หุบ Viper →  Areal Skill 3 → Nathenn ตีธรรมดา Asal + หาจังหวะ Execute Asal [ลำดับการฆ่า Asal, Valerian, Viper] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Asal → Lowan Skill 3 ใส่ Sharon → Luvia Skill 2 → Lowan ตีธรรมดา Sharon  ไปเรื่อยๆจนตาย แล้วเปลี่ยนมา Skill ใส่ Areal + Luvia คอยหุบ Asal [ลำดับการฆ่า Sharon, Areal, Asal] </t>
+  </si>
+  <si>
+    <t>Oryes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Oryes → Lily Skill 2 ดึง Asal → Valerian Skill 3 → Asal Skill 2 เล็ง Oryes → Lily Skill 3 → เน้นจัดการ Oryes ก่อน [ลำดับการฆ่า Oryes, Valerian, Kokardi] </t>
+  </si>
+  <si>
+    <t>Sharon (เร็วสุด) Skill 3 ใส่ Ray → Sania Skill 3 ให้ Tiamat → Tiamat ตีธรรมดา Viper → Sharon ธรรมดา Viper → Sania ธรรมดา Fiamelia → รอให้ Tiamat เปลี่ยนร่าง แล้ว Sania Skill 3 ให้ Tiamat [ลำดับการฆ่า Fiamelia, Viper, Raymerry] ***ทีมนี้เสี่ยงเนื่องจาก Viper กับ Ray คอยสวนตลอด ***</t>
+  </si>
+  <si>
+    <t>Palin (เร็วสุด) Skill 3 ให้ Tiamat → Sania Skill 3 ให้ Tiamat → Tiamat Skill 2 → รอ Tiamat เปลี่ยนร่าง → Sania &amp; Palin เน้นบัฟให้ Tiamat และไม่ตีให้ Tiamat ฝั่งตรงข้ามสวน</t>
+  </si>
+  <si>
+    <t>Tsukiyo Mi (เร็วสุด) Skill 3 ดึง Massiah → Massiah ปาด (Build: Fury,Keeneye,Furyedge) → Beyotin Skill 2 ดึง Massiah ปาด → Tsukiyo Mi Skill 3 ดึง Massiah → Massiah Skill 2 ใส่ Sharon → Beyotin Skill 2 ดึง Massiah ปาด → Tsukiyo Mi Skill 2 →  Beyotin Skill 3 → Massiah Skill 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Viper → Lowan Skill 3 ใส่ Nathenn → Areal Skill 3 → Luvia Skill 2 → Lowan ตีธรรมดาหรือ Skill 3 ใส่ Nathenn ไปเรื่อยๆ จนตาย (เพื่อเก็บ Stack ให้ Shell Ouroboros) + Luvia คอยหุบ Viper [ลำดับการฆ่า Nathenn, Viper, Areal]  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Valerian (เพื่อให้ Airon ทีมศัตรู บัฟ Valerian) → Lily Skill 2 ดึง Asal → Valerian Skill 3 → Asal Skill 2 เล็ง Valerian → Lily Skill 3 → Asal Skill 3 ใส่ Asal → Lily ตีธรรมดาใส่ Asal → Asal Skill 2 ใส่ Asal → Lily Skill 2 ดึง Asal → Asal ตีธรรมดา Airon แล้วไล่ฆ่าตามลำดับ [ลำดับการฆ่า Airon, Valerian, Asal] </t>
+  </si>
+  <si>
+    <t>Nathenn (เร็วสุด) ตีธรรมดา Sylvia → Sylvia Reset → Buff Nathenn → Kethos Skill 2 → หาจังหวะ Execute Nathenn [ลำดับการฆ่า Nathenn, Kethos, Sylvia]</t>
+  </si>
+  <si>
+    <t>Nathenn (เร็วสุด) ตีธรรมดา Sylvia → Sylvia Reset → Buff Kethos → Nathenn Skill 3 → Kethos Skill 2 ใส่ Nathenn + Skill 3 ใส่ Nathenn → หาจังหวะ Execute Nathenn [ลำดับการฆ่า Nathenn, XC, Sylvia]</t>
+  </si>
+  <si>
+    <t>Luvia (เร็วสุด) หุบ Areal → Lowan Skill 3 ใส่ Sharon → Areal Skill 3 → Luvia Skill 2 → Lowan ตีธรรมดา ใส่ Sharon ไปเรื่อยๆ จนตาย (เพื่อเก็บ Stack ให้ Shell Ouroboros) + Luvia คอยหุบ Areal [ลำดับการฆ่า Sharon, XC, Areal]</t>
+  </si>
+  <si>
+    <t>Nathenn (เร็วสุด) ตีธรรมดา Sania → Sylvia Reset → Buff Kethos → Nathenn Skill 3 → Kethos Skill 3 ใส่ Sania → Nathenn หาจังหวะ Execute Sania [ลำดับการฆ่า Sania, Nathenn, Kethos]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Asal → Lily Skill 2 ดึง Asal → Sania Skill 3 ให้ Asal → Asal ตีธรรมดา Asal จน Stack = 8 แล้วเปลี่ยนไปตี Fuqiu  [ลำดับการฆ่า Fuqiu, Viper, Asal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doki (เร็วสุด) Skill 3 → Gianc Skill 3 ใส่ XL → Fiamelia Skill 3 → Doki  Skill 2 → Gianc Skill 3 → Fiamelia Skill 3 [ลำดับการฆ่า XL, Plume, Fiamelia] </t>
+  </si>
+  <si>
+    <t>Tsukiyo Mi (เร็วสุด) Skill 3 ดึง Massiah → Massiah ปาด (Build: Fury,Keeneye,Furyedge) → Beyotin Skill 2 ดึง Massiah ปาด → Tsukiyo Mi Skill 3 ดึง Massiah → Massiah Skill 2 → Beyotin Skill 2 ดึง Massiah ปาด</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Tiamat → Lily Skill 2 ดึง Asal → Sania Skill 3 ให้ Asal → Asal Skill 2 หรือตีธรรมดาจน Tiamat มี Stack ≈ 10 แล้วย้ายไปฆ่า Fiamelia ก่อน [ลำดับการฆ่า Fiamelia, Tiamat, Asal] </t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset → Buff Kethos → Nathenn Skill 3 → Kethos Skill 2 ใส่ Lowan → Nathenn ตีธรรมดา Lowan → Kethos Skill 3 ใส่ Sania → Nathenn Execute Lowan [ลำดับการฆ่า Lowan, Sania, Kethos]</t>
+  </si>
+  <si>
+    <t>Palin Skill 3 ให้ Tiamat → Sania Skill 3 ให้ Tiamat → Tiamat Skill 2 → รอ Tiamat เปลี่ยนร่าง → Sania &amp; Palin เน้นบัฟให้ Tiamat และไม่ตีให้ Raymerry ฝั่งตรงข้ามสวน</t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset → Buff Luvia → Luvia หุบ Areal → Nathenn Skill 3 → Nathenn ตีธรรมดา Nathenn เพื่อรอจังหวะ Execute [ลำดับการฆ่า Nathenn, Viper, Areal]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plume (เร็วสุด) Skill 3 → Nevette Skill 3 → Ray Skill 3 → ซ้ำอีกรอบ + ให้ Ray Execute Lowan </t>
+  </si>
+  <si>
+    <t>Asal (เร็วสุด) Skill 3 ใส่ Sania → Lily Skill 2 ดึง Asal → Sania Skill 3 ให้ Asal → Asal Skill 2 หรือตีธรรมดาจน Sania เพิ่ม Stack ไปเรื่อยๆเพื่อฆ่า Sania ก่อน [ลำดับการฆ่า Sania, Viper, Asal] **ทีมนี้ใช้เวลาเล่นนานหน่อย**</t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset → Buff Kethos → Nathenn Skill 3 → Kethos Skill 2 ใส่ Nathenn → Nathenn ตีธรรมดา Nathenn → Kethos Skill 3 ใส่ XL → Nathenn Execute Nathenn [ลำดับการฆ่า Nathenn, XL, Valerian]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan Skill 3 ใส่ Kethos →  Areal Skill 3 →  XL Skill 3 → Lowan Skill 2 ใส่ Kethos → เน้นจัดการ Kethos ก่อน จากนั้นค่อยให้ Lowan ค่อย Skill 3 ใส่ Lowan [ลำดับการฆ่า Kethos, Lowan, Areal] </t>
+  </si>
+  <si>
+    <t>Asal (เร็วสุด) Skill 3 ใส่ XL → Lily Skill 2 ดึง Asal → Sania Skill 3 ให้ Asal → Asal Skill 2 หรือตีธรรมดาจน XL เพิ่ม Stack ไปเรื่อยๆเพื่อฆ่า XL ก่อน [ลำดับการฆ่า XL, Fiamelia, Viper]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doki (เร็วสุด) Skill 3 → Liliam Skill 3 ใส่ XC → Ray Execute XC  → Liliam ตีธรรมดาเพื่อเพิ่มเลือดรอ Skill 3 ใส่ Kethos [ลำดับการฆ่า XC, Kethos, Sania] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asal (เร็วสุด) Skill 3 ใส่ Tiamat → Arel Skill 3 → Valerian Skill 3 → Asal เน้นตี Tiamat ให้มี Stack เพื่อลดดาเมจ และฆ่า Tiamat ก่อน [ลำดับการฆ่า Tiamat, Lowan, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan Skill 3 ใส่ Sania → Gianc Skill 3 ใส่ Sania → Areal Skill 3 → Lowan Skill 2 ใส่ Sania → Gianc Skill 2 ใส่ Sania [ลำดับการฆ่า Sania, Tiamat, Palin] </t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset → Buff Liliam → Piayera Skill 3 + Skill 2 → Liliam Skill 3 ใส่ XC → Sylvia ตีธรรมดา XC → Piayera Skill 3 + ตีธรรมดา Fiamelia → Sylvia ตีธรรมดา Fiamelia → Liliam Skill 2 ใส่ Sharon [ลำดับการฆ่า XC, Sharon, Fiamelia]</t>
+  </si>
+  <si>
+    <t>Nathenn (เร็วสุด) Skill 3 → Asal Skill 3 ใส่ Lowan → Areal Skill 3 → Nathenn ตีธรรมดา Lowan → Asal Skill 2 ใส่ Lowan → หาจังหวะ Execute Lowan [ลำดับการฆ่า Lowan, XL, Areal]</t>
+  </si>
+  <si>
+    <t>Valerian Skill 3 → Sharon Skill 3 → XC Skill 3 → เน้นฆ่า Massiah ก่อน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan (เร็วสุด) Skill 3 ใส่ Lowan → XL Skill 3 → Lingluo Skill 2 → Lowan Skill 2 ใส่ Lowan → เน้นฆ่า Lowan ก่อน [ลำดับการฆ่า Lowan, Raymerry, Lingluo] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvia (เร็วสุด) Reset + Buff Piayera → Sharon Skill 3 → Piayera Skill 3 + ตีธรรมดา Sylvia → Sharon Skill 3 → Piayera Skill 3 + Buff [ลำดับการฆ่า XL, Sylvia, Luvia] </t>
   </si>
 </sst>
 </file>
@@ -1753,7 +1856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1817,6 +1920,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1988,7 +2094,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="102">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="103">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -2395,6 +2501,10 @@
   </rv>
   <rv s="0">
     <v>101</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>102</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -2513,6 +2623,7 @@
   <rel r:id="rId100"/>
   <rel r:id="rId101"/>
   <rel r:id="rId102"/>
+  <rel r:id="rId103"/>
 </richValueRels>
 </file>
 
@@ -2833,7 +2944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F8EE7B-7B28-4194-BF71-6AB7143EE20B}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" style="10" bestFit="1" customWidth="1"/>
@@ -3393,23 +3504,23 @@
     </row>
     <row r="51" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="26" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="1" t="e" vm="74">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
+      <c r="B52" s="1" t="e" vm="75">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="B52" s="1" t="e" vm="75">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="B53" s="1" t="e" vm="76">
         <v>#VALUE!</v>
@@ -3417,7 +3528,7 @@
     </row>
     <row r="54" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B54" s="1" t="e" vm="77">
         <v>#VALUE!</v>
@@ -3425,7 +3536,7 @@
     </row>
     <row r="55" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="1" t="e" vm="78">
         <v>#VALUE!</v>
@@ -3433,7 +3544,7 @@
     </row>
     <row r="56" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B56" s="1" t="e" vm="79">
         <v>#VALUE!</v>
@@ -3441,7 +3552,7 @@
     </row>
     <row r="57" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="1" t="e" vm="80">
         <v>#VALUE!</v>
@@ -3449,7 +3560,7 @@
     </row>
     <row r="58" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B58" s="1" t="e" vm="81">
         <v>#VALUE!</v>
@@ -3457,7 +3568,7 @@
     </row>
     <row r="59" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B59" s="1" t="e" vm="82">
         <v>#VALUE!</v>
@@ -3465,7 +3576,7 @@
     </row>
     <row r="60" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B60" s="1" t="e" vm="83">
         <v>#VALUE!</v>
@@ -3473,7 +3584,7 @@
     </row>
     <row r="61" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B61" s="1" t="e" vm="84">
         <v>#VALUE!</v>
@@ -3481,7 +3592,7 @@
     </row>
     <row r="62" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B62" s="1" t="e" vm="85">
         <v>#VALUE!</v>
@@ -3489,7 +3600,7 @@
     </row>
     <row r="63" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B63" s="1" t="e" vm="86">
         <v>#VALUE!</v>
@@ -3497,7 +3608,7 @@
     </row>
     <row r="64" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B64" s="1" t="e" vm="87">
         <v>#VALUE!</v>
@@ -3505,7 +3616,7 @@
     </row>
     <row r="65" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B65" s="1" t="e" vm="88">
         <v>#VALUE!</v>
@@ -3513,23 +3624,23 @@
     </row>
     <row r="66" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="1" t="e" vm="89">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B66" s="1" t="e" vm="89">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="8" t="s">
+      <c r="B67" s="1" t="e" vm="90">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="B67" s="1" t="e" vm="90">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="B68" s="1" t="e" vm="91">
         <v>#VALUE!</v>
@@ -3537,7 +3648,7 @@
     </row>
     <row r="69" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B69" s="1" t="e" vm="92">
         <v>#VALUE!</v>
@@ -3545,7 +3656,7 @@
     </row>
     <row r="70" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B70" s="1" t="e" vm="93">
         <v>#VALUE!</v>
@@ -3553,7 +3664,7 @@
     </row>
     <row r="71" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B71" s="1" t="e" vm="94">
         <v>#VALUE!</v>
@@ -3561,7 +3672,7 @@
     </row>
     <row r="72" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B72" s="1" t="e" vm="95">
         <v>#VALUE!</v>
@@ -3569,7 +3680,7 @@
     </row>
     <row r="73" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B73" s="1" t="e" vm="96">
         <v>#VALUE!</v>
@@ -3577,7 +3688,7 @@
     </row>
     <row r="74" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" s="1" t="e" vm="97">
         <v>#VALUE!</v>
@@ -3585,7 +3696,7 @@
     </row>
     <row r="75" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B75" s="1" t="e" vm="98">
         <v>#VALUE!</v>
@@ -3593,23 +3704,23 @@
     </row>
     <row r="76" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B76" s="9" t="e" vm="99">
+        <v>99</v>
+      </c>
+      <c r="B76" s="1" t="e" vm="99">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B77" s="1" t="e" vm="100">
+        <v>100</v>
+      </c>
+      <c r="B77" s="9" t="e" vm="100">
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B78" s="1" t="e" vm="101">
         <v>#VALUE!</v>
@@ -3617,9 +3728,17 @@
     </row>
     <row r="79" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="1" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B79" s="1" t="e" vm="102">
+      <c r="B80" s="1" t="e" vm="103">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3631,7 +3750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8DF62-D3A8-45C5-B4BC-03270E337BE8}">
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="18" bestFit="1" customWidth="1"/>
@@ -3810,7 +3929,7 @@
         <v>29</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -3851,7 +3970,7 @@
         <v>7</v>
       </c>
       <c r="M5" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -3892,7 +4011,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -3933,7 +4052,7 @@
         <v>19</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -3974,7 +4093,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4015,7 +4134,7 @@
         <v>13</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4056,7 +4175,7 @@
         <v>13</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4097,7 +4216,7 @@
         <v>23</v>
       </c>
       <c r="M11" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -4138,7 +4257,7 @@
         <v>7</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4179,7 +4298,7 @@
         <v>13</v>
       </c>
       <c r="M13" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4220,7 +4339,7 @@
         <v>29</v>
       </c>
       <c r="M14" s="25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4261,7 +4380,7 @@
         <v>13</v>
       </c>
       <c r="M15" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4302,7 +4421,7 @@
         <v>13</v>
       </c>
       <c r="M16" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4343,7 +4462,7 @@
         <v>13</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4384,7 +4503,7 @@
         <v>19</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -4425,7 +4544,7 @@
         <v>41</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4466,7 +4585,7 @@
         <v>13</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -4507,7 +4626,7 @@
         <v>35</v>
       </c>
       <c r="M21" s="25" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4548,7 +4667,7 @@
         <v>13</v>
       </c>
       <c r="M22" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4589,7 +4708,7 @@
         <v>3</v>
       </c>
       <c r="M23" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4630,7 +4749,7 @@
         <v>13</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4671,7 +4790,7 @@
         <v>29</v>
       </c>
       <c r="M25" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4712,7 +4831,7 @@
         <v>35</v>
       </c>
       <c r="M26" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4753,7 +4872,7 @@
         <v>35</v>
       </c>
       <c r="M27" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4794,7 +4913,7 @@
         <v>13</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4835,7 +4954,7 @@
         <v>27</v>
       </c>
       <c r="M29" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4876,7 +4995,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -4917,7 +5036,7 @@
         <v>29</v>
       </c>
       <c r="M31" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -4958,7 +5077,7 @@
         <v>13</v>
       </c>
       <c r="M32" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4999,7 +5118,7 @@
         <v>29</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5040,7 +5159,7 @@
         <v>23</v>
       </c>
       <c r="M34" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5081,7 +5200,7 @@
         <v>35</v>
       </c>
       <c r="M35" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5122,7 +5241,7 @@
         <v>19</v>
       </c>
       <c r="M36" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5163,7 +5282,7 @@
         <v>29</v>
       </c>
       <c r="M37" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5204,7 +5323,7 @@
         <v>19</v>
       </c>
       <c r="M38" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5245,7 +5364,7 @@
         <v>7</v>
       </c>
       <c r="M39" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5286,7 +5405,7 @@
         <v>35</v>
       </c>
       <c r="M40" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5327,7 +5446,7 @@
         <v>35</v>
       </c>
       <c r="M41" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5368,7 +5487,7 @@
         <v>35</v>
       </c>
       <c r="M42" s="25" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5409,7 +5528,7 @@
         <v>13</v>
       </c>
       <c r="M43" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5450,7 +5569,7 @@
         <v>15</v>
       </c>
       <c r="M44" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5491,7 +5610,7 @@
         <v>15</v>
       </c>
       <c r="M45" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5532,7 +5651,7 @@
         <v>19</v>
       </c>
       <c r="M46" s="25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5573,7 +5692,7 @@
         <v>43</v>
       </c>
       <c r="M47" s="25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5614,7 +5733,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5655,7 +5774,7 @@
         <v>11</v>
       </c>
       <c r="M49" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5696,7 +5815,7 @@
         <v>7</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5737,7 +5856,7 @@
         <v>29</v>
       </c>
       <c r="M51" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5778,7 +5897,7 @@
         <v>27</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5819,7 +5938,7 @@
         <v>23</v>
       </c>
       <c r="M53" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5860,7 +5979,7 @@
         <v>27</v>
       </c>
       <c r="M54" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5901,7 +6020,7 @@
         <v>43</v>
       </c>
       <c r="M55" s="25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
@@ -5942,7 +6061,7 @@
         <v>15</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -5983,7 +6102,7 @@
         <v>7</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6024,7 +6143,7 @@
         <v>29</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
@@ -6065,7 +6184,7 @@
         <v>35</v>
       </c>
       <c r="M59" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6106,7 +6225,7 @@
         <v>7</v>
       </c>
       <c r="M60" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6147,7 +6266,7 @@
         <v>35</v>
       </c>
       <c r="M61" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6188,7 +6307,7 @@
         <v>13</v>
       </c>
       <c r="M62" s="25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6229,7 +6348,7 @@
         <v>11</v>
       </c>
       <c r="M63" s="25" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6270,7 +6389,7 @@
         <v>23</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -6311,7 +6430,7 @@
         <v>7</v>
       </c>
       <c r="M65" s="25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6352,7 +6471,7 @@
         <v>11</v>
       </c>
       <c r="M66" s="25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -6393,7 +6512,7 @@
         <v>35</v>
       </c>
       <c r="M67" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6434,7 +6553,7 @@
         <v>27</v>
       </c>
       <c r="M68" s="25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6475,7 +6594,7 @@
         <v>29</v>
       </c>
       <c r="M69" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6516,7 +6635,7 @@
         <v>35</v>
       </c>
       <c r="M70" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -6598,7 +6717,7 @@
         <v>13</v>
       </c>
       <c r="M72" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -6639,246 +6758,1279 @@
         <v>29</v>
       </c>
       <c r="M73" s="25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="G74" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H74" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J74" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K74" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L74" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M74" s="25" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A74" s="20"/>
-      <c r="B74" s="21"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="23"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="22"/>
-      <c r="K74" s="23"/>
-      <c r="L74" s="22"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
-      <c r="B75" s="21"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="22"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="20"/>
-      <c r="B76" s="21"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="22"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="22"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="20"/>
-      <c r="B77" s="21"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="23"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="22"/>
-      <c r="K77" s="23"/>
-      <c r="L77" s="22"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A78" s="20"/>
-      <c r="B78" s="21"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="23"/>
-      <c r="L78" s="22"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A79" s="20"/>
-      <c r="B79" s="21"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="21"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="23"/>
-      <c r="L79" s="22"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A80" s="20"/>
-      <c r="B80" s="21"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="22"/>
-      <c r="K80" s="23"/>
-      <c r="L80" s="22"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="20"/>
-      <c r="B81" s="21"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="23"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="22"/>
-      <c r="K81" s="23"/>
-      <c r="L81" s="22"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="20"/>
-      <c r="B82" s="21"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="23"/>
-      <c r="L82" s="22"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="23"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="22"/>
-      <c r="K83" s="23"/>
-      <c r="L83" s="22"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="20"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="21"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="23"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="22"/>
-      <c r="K84" s="23"/>
-      <c r="L84" s="22"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="20"/>
-      <c r="B85" s="21"/>
-      <c r="C85" s="20"/>
-      <c r="D85" s="21"/>
-      <c r="E85" s="20"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="23"/>
-      <c r="H85" s="22"/>
-      <c r="I85" s="23"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="23"/>
-      <c r="L85" s="22"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="20"/>
-      <c r="B86" s="21"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="21"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="22"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="23"/>
-      <c r="L86" s="22"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="20"/>
-      <c r="B87" s="21"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="20"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="23"/>
-      <c r="J87" s="22"/>
-      <c r="K87" s="23"/>
-      <c r="L87" s="22"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
-      <c r="B88" s="21"/>
-      <c r="C88" s="20"/>
-      <c r="D88" s="21"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="21"/>
-      <c r="G88" s="23"/>
-      <c r="H88" s="22"/>
-      <c r="I88" s="23"/>
-      <c r="J88" s="22"/>
-      <c r="K88" s="23"/>
-      <c r="L88" s="22"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="20"/>
-      <c r="B89" s="21"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="21"/>
-      <c r="E89" s="20"/>
-      <c r="F89" s="21"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="22"/>
-      <c r="I89" s="23"/>
-      <c r="J89" s="22"/>
-      <c r="K89" s="23"/>
-      <c r="L89" s="22"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="20"/>
-      <c r="B90" s="21"/>
-      <c r="C90" s="20"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="20"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="22"/>
-      <c r="I90" s="23"/>
-      <c r="J90" s="22"/>
-      <c r="K90" s="23"/>
-      <c r="L90" s="22"/>
+    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H75" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K75" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L75" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A76" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J76" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="L76" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" s="25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H77" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="J77" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K77" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L77" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M77" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H78" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I78" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="J78" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L78" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M78" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H79" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I79" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J79" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="K79" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="L79" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M79" s="25" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A80" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H80" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J80" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K80" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L80" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M80" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G81" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H81" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I81" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J81" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L81" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="M81" s="25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I82" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J82" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="K82" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="L82" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M82" s="25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A83" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D83" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="J83" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="L83" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M83" s="25" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A84" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E84" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G84" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H84" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K84" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="L84" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M84" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A85" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H85" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="J85" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K85" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="L85" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="M85" s="25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G86" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H86" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I86" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="J86" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="K86" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L86" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M86" s="25" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A87" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E87" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F87" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="H87" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I87" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K87" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="L87" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M87" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A88" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H88" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J88" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L88" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M88" s="25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A89" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H89" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="J89" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="K89" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L89" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M89" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A90" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F90" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="G90" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H90" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J90" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K90" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M90" s="25" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A91" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F91" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G91" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H91" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="J91" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K91" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L91" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M91" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A92" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G92" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H92" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I92" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J92" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K92" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L92" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M92" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A93" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F93" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="H93" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="J93" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K93" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="L93" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M93" s="25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G94" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H94" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J94" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K94" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L94" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M94" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A95" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H95" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I95" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="J95" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="K95" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="L95" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="M95" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A96" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F96" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H96" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="J96" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K96" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="L96" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M96" s="19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F97" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G97" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H97" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I97" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J97" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K97" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="L97" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M97" s="25" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A98" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H98" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J98" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K98" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L98" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M98" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D99" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H99" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J99" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K99" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="L99" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M99" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D100" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H100" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="J100" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K100" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="L100" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="25" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A101" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F101" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G101" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="J101" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K101" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="L101" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="25" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D102" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="F102" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H102" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I102" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="J102" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="K102" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L102" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="M102" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A103" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="F103" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G103" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H103" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="I103" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="J103" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K103" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L103" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M103" s="25" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A104" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F104" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H104" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="J104" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K104" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="L104" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M104" s="25" t="s">
+        <v>216</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6887,15 +8039,15 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CA26D47E-6623-4B72-A42C-17472717221A}">
           <x14:formula1>
-            <xm:f>Information!$A$1:$A$79</xm:f>
+            <xm:f>Information!$A$1:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>K2:K90 I2:I90 G2:G90 A2:A90 C2:C90 E2:E90</xm:sqref>
+          <xm:sqref>C2:C104 A2:A104 I2:I104 G2:G104 K2:K104 E2:E104</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L90 J2:J90 H2:H90 B2:B90 D2:D90 F2:F90</xm:sqref>
+          <xm:sqref>B2:B104 D2:D104 F2:F104 H2:H104 L2:L104 J2:J104</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1149" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4BD0B21-9AE5-45AD-86C4-A02264C521EE}"/>
+  <xr:revisionPtr revIDLastSave="1287" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD160F3-FEAB-4A13-9539-59F721109DC0}"/>
   <bookViews>
-    <workbookView xWindow="-84" yWindow="1116" windowWidth="10320" windowHeight="10524" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="1" r:id="rId1"/>
@@ -1082,7 +1082,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="224">
   <si>
     <t>Animus</t>
   </si>
@@ -1733,6 +1733,27 @@
   </si>
   <si>
     <t xml:space="preserve">Sylvia (เร็วสุด) Reset + Buff Piayera → Sharon Skill 3 → Piayera Skill 3 + ตีธรรมดา Sylvia → Sharon Skill 3 → Piayera Skill 3 + Buff [ลำดับการฆ่า XL, Sylvia, Luvia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heinrich (เร็วสุด) Skill 2 → Obol Skill 3 → Sharon Skill 3 → ทำซ้ำอีกรอบแล้วไล่ฆ่าทีละตัว [ลำดับการฆ่า Gianc, Areal, Holden] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turandot (เร็วสุด) Skill 3 → Gianc Skill 3 ใส่ XC → Nathenn Execute XC → Nathenn Skill 3 → Turandot Skill 3 → Nathenn ตีธรรมดา Fiamelia → Gianc ตีธรรมดา Fiamelia → Nathenn หาจังหวะ Execute Fiamelia [ลำดับการฆ่า XC, Fiamelia, Raymerry] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sylvia (เร็วสุด) Reset + Buff XL → Nevette Skill 3 →  XL Skill 3 + Sylvia ตีธรรมดา Piayera → Nevette Skill 3 เล็ง Piayera → XL Skill 2 [ลำดับการฆ่า Piayera, Valerian, Asal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Nathenn → Lowan Skill 3 ใส่ Sharon → Areal Skill 3 → Lowan ตีธรรมดา Sharon ไปเรื่อยๆ จนตาย เพื่อเก็บ Stack Shell Ouroboros → Luvia คอยหุบ Nathenn [ลำดับการฆ่า Sharon, Areal, Nathenn] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airon (เร็วสุด) Skill 2 ให้ Liliam และ ตีธรรมดา ใส่ Sharon → Liliam Skill 3 ใส่ Sharon → Valerian Skill 3 → Airon Skill 3 ใส่ Raymerry → Liliam ตีธรรมดา Fiamelia เพื่อรอ CD แล้ว Skill 3 ใส่ Raymerry [ลำดับการฆ่า Sharon, Raymerry, Fiamelia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XC (เร็วสุด) Skill 3 → Nevette Skill 3 → Santik Skill 2 →  XC ตีธรรมดา Piayera → Nevette Skill 3 [ลำดับการฆ่า Piayera, Valerian, Asal] </t>
+  </si>
+  <si>
+    <t>Palin (เร็วสุด) Skill 3 ให้ Tiamat → Lingluo Skill 2 → Tiamat ตีธรรมดา Kethos เพื่อรอเปลี่ยนร่าง → Lingluo กับ Palin คอยบัฟเสริม</t>
   </si>
 </sst>
 </file>
@@ -3750,7 +3771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8DF62-D3A8-45C5-B4BC-03270E337BE8}">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="18" bestFit="1" customWidth="1"/>
@@ -8032,6 +8053,293 @@
         <v>216</v>
       </c>
     </row>
+    <row r="105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A105" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F105" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H105" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I105" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J105" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K105" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="L105" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M105" s="25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A106" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G106" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H106" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I106" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="J106" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="L106" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="M106" s="25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A107" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E107" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="H107" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="J107" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="K107" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L107" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M107" s="25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A108" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F108" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="H108" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I108" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="J108" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K108" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L108" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="M108" s="25" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D109" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E109" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F109" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G109" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="H109" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="J109" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K109" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L109" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="M109" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A110" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C110" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E110" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H110" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="I110" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="J110" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="L110" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="M110" s="25" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A111" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D111" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F111" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="G111" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="H111" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I111" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="J111" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="K111" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="L111" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="M111" s="25" t="s">
+        <v>223</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -8041,13 +8349,13 @@
           <x14:formula1>
             <xm:f>Information!$A$1:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C104 A2:A104 I2:I104 G2:G104 K2:K104 E2:E104</xm:sqref>
+          <xm:sqref>C2:C111 A2:A111 G2:G111 K2:K111 E2:E111 I2:I111</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B104 D2:D104 F2:F104 H2:H104 L2:L104 J2:J104</xm:sqref>
+          <xm:sqref>B2:B111 F2:F111 H2:H111 L2:L111 J2:J111 D2:D111</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/etheria_restart.xlsx
+++ b/etheria_restart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvg-fight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1287" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACD160F3-FEAB-4A13-9539-59F721109DC0}"/>
+  <xr:revisionPtr revIDLastSave="1494" documentId="13_ncr:1_{BB734052-C730-434C-A607-24951B158975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{124FF5F0-8417-4270-B4E4-9E7E94E45698}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{7D89B41E-7404-47EB-B8F5-ABCE13AB4321}"/>
   </bookViews>
@@ -1082,7 +1082,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="235">
   <si>
     <t>Animus</t>
   </si>
@@ -1754,6 +1754,39 @@
   </si>
   <si>
     <t>Palin (เร็วสุด) Skill 3 ให้ Tiamat → Lingluo Skill 2 → Tiamat ตีธรรมดา Kethos เพื่อรอเปลี่ยนร่าง → Lingluo กับ Palin คอยบัฟเสริม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiamelia Skill 3 → Liliam Skill 3 ใส่ Piayera → Fiamelia &amp; Liliam ตีธรรมดา Sharon → Liliam Skill 2 ใส่ Sharon [ลำดับการฆ่า Piayera, Sharon, Fiamelia] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan Skill 3 ใส่ Kethos → XL Skill 3 → Areal Skill 3 → Areal Skill 2 → XL Skill 2 ใส่ Kethos → Lowan Skill 2 ใส่ Kethos → หลัง Kethos ตาย ค่อยให้ Lowan Skill 3 ใส่ Nathenn [ลำดับการฆ่า Kethos, Nathenn, Areal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Asal → Asal Skill 3 ใส่ XL → Danvery Skill 3 ใส่ Valerian → Luvia Skill 2 → Asal Skill 2 ใส่ XL → Danvery Skill 2 → เน้นจัดการ XL ก่อน โดยให้ Luvia คอยหุบ Asal [ลำดับการฆ่า XL, Valerian, Asal] </t>
+  </si>
+  <si>
+    <t>Piayera (เร็วสุด) Skill 3 +  Skill 3 → Viper Skill 3 → XC กับ Viper ตีธรรมดา Lowan → Piayera Skill 2 → XC Skill 3 → เน้นจัดการ Lowan ก่อน [ลำดับการฆ่า Lowan, Sylvia, XC]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharon (เร็วสุด) Skill 3 → Diting Skill 3 ใส่ Ray → Fuqiu Skill 3 → Sharon ตีธรรมดา Dan → Diting Skill 2 ใส่ Ray → เน้นกระจายแปะ DOT ไปเรื่อยๆ [ลำดับการฆ่า Raymerry, Sania, Danvery] </t>
+  </si>
+  <si>
+    <t>Turandot (เร็วสุด) Skill 3 → XC Skill 3 → Qano Skill 3 (ค่า Speed แนะนำ XC = 350, Qano = 310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doki (เร็วสุด) Skill 3 → Asal Skill 3 ใส่ XC → Lingluo + Doki ตีธรรมดา XL → Lingluo Skill 3 → Asal Skill 2 ใส่ XC [ลำดับการฆ่า XC, Sania, Plume] </t>
+  </si>
+  <si>
+    <t>Sylvia (เร็วสุด) Reset + ตีธรรมดา Massiah → XC Skill 3 → Sylvia Skill 2 ให้ XC → XC ตีธรรมดา Massiah [ลำดับการฆ่า Massiah, Turandot, Valerian]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luvia (เร็วสุด) หุบ Asal → Sharon Skill 3 → Fuqiu Skill 3 → Sharon ตี Tiamat → Luvia Skill 2 → Sharon ตี Tiamat → เน้นฆ่า Tiamat กับ Sania ก่อน โดยให้ Luvia คอยหุบ Areal [ลำดับการฆ่า Tiamat, Sania, Asal] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowan Skill 3 ใส่ Sylvia (เน้นจัดการ Sylvia ก่อน) → Kethos Skill 3 ใส่ Dan → Lowan Skill 3 ใส่ Dan → Areal Skill 3 → Kethos Skill 2 → Lowan ตีธรรมดา Dan → หลัง Dan ตาย ค่อยให้ Lowan Skill 3 ใส่ Nathenn [ลำดับการฆ่า Sylvia, Danvery, Nathenn] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danvery (เร็วสุด) Skill 3 ใส่ Areal → Asal Skill 3 ใส่ XL → Lingluo ตีธรรดา → Danvery Skill 2 → Dan คอยตีดึงเกจ Aseal → Asal Skill 2 → Lingluo Skill 2 → เน้นจัดการ XL เป็นหลัก [ลำดับการฆ่า XL, Luvia, Areal] </t>
   </si>
 </sst>
 </file>
@@ -1877,7 +1910,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1921,9 +1954,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1934,9 +1964,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3527,7 +3554,7 @@
       <c r="A51" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B51" s="26" t="e" vm="74">
+      <c r="B51" s="24" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
     </row>
@@ -3771,7 +3798,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C8DF62-D3A8-45C5-B4BC-03270E337BE8}">
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" style="18" bestFit="1" customWidth="1"/>
@@ -3786,4558 +3813,5009 @@
     <col min="10" max="10" width="14.33203125" style="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.33203125" style="16" customWidth="1"/>
     <col min="12" max="12" width="16.5546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="55.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="72.88671875" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="23" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="23" t="s">
+      <c r="F2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="25" t="s">
+      <c r="M2" s="23" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+    <row r="3" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="23" t="s">
+      <c r="H3" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J3" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="23" t="s">
+      <c r="J3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="25" t="s">
+      <c r="M3" s="23" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="20" t="s">
+      <c r="D4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="23" t="s">
+      <c r="F4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J4" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="23" t="s">
+      <c r="J4" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L4" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="25" t="s">
+      <c r="L4" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="23" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="23" t="s">
+      <c r="F5" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="23" t="s">
+      <c r="H5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="25" t="s">
+      <c r="L5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M5" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="D6" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="23" t="s">
+      <c r="H6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="23" t="s">
+      <c r="J6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="23" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="23" t="s">
+      <c r="F7" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="23" t="s">
+      <c r="H7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="22" t="s">
+      <c r="L7" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="23" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="20" t="s">
+      <c r="D8" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="23" t="s">
+      <c r="F8" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="23" t="s">
+      <c r="H8" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J8" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="23" t="s">
+      <c r="J8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="25" t="s">
+      <c r="L8" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="23" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="J9" s="22" t="s">
+      <c r="J9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L9" s="22" t="s">
+      <c r="L9" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="25" t="s">
+      <c r="M9" s="23" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="23" t="s">
+      <c r="F10" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="L10" s="22" t="s">
+      <c r="L10" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="20" t="s">
+      <c r="D11" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="23" t="s">
+      <c r="F11" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="23" t="s">
+      <c r="H11" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J11" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="L11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="25" t="s">
+      <c r="M11" s="23" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="20" t="s">
+      <c r="D12" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M12" s="25" t="s">
+      <c r="L12" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M12" s="23" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="20" t="s">
+      <c r="D13" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="23" t="s">
+      <c r="F13" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="J13" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K13" s="23" t="s">
+      <c r="J13" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="22" t="s">
+      <c r="L13" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M13" s="25" t="s">
+      <c r="M13" s="23" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="23" t="s">
+      <c r="F14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="J14" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="23" t="s">
+      <c r="J14" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="L14" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M14" s="25" t="s">
+      <c r="L14" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="23" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="23" t="s">
+      <c r="H15" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J15" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K15" s="23" t="s">
+      <c r="J15" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="L15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M15" s="25" t="s">
+      <c r="M15" s="23" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="23" t="s">
+      <c r="F16" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="L16" s="22" t="s">
+      <c r="L16" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M16" s="25" t="s">
+      <c r="M16" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="20" t="s">
+      <c r="D17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I17" s="23" t="s">
+      <c r="H17" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="J17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="L17" s="22" t="s">
+      <c r="L17" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M17" s="25" t="s">
+      <c r="M17" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+    <row r="18" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="20" t="s">
+      <c r="D18" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="23" t="s">
+      <c r="F18" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="23" t="s">
+      <c r="H18" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J18" s="22" t="s">
+      <c r="J18" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L18" s="22" t="s">
+      <c r="L18" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M18" s="25" t="s">
+      <c r="M18" s="23" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="20" t="s">
+      <c r="B19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="20" t="s">
+      <c r="D19" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="23" t="s">
+      <c r="F19" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="23" t="s">
+      <c r="H19" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="J19" s="22" t="s">
+      <c r="J19" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="K19" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="L19" s="22" t="s">
+      <c r="L19" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M19" s="25" t="s">
+      <c r="M19" s="23" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="23" t="s">
+      <c r="F20" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="23" t="s">
+      <c r="H20" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="23" t="s">
+      <c r="J20" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="22" t="s">
+      <c r="L20" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M20" s="25" t="s">
+      <c r="M20" s="23" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G21" s="23" t="s">
+      <c r="F21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J21" s="22" t="s">
+      <c r="J21" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="L21" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M21" s="25" t="s">
+      <c r="L21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M21" s="23" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="20" t="s">
+      <c r="B22" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="20" t="s">
+      <c r="D22" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="22" t="s">
+      <c r="L22" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M22" s="25" t="s">
+      <c r="M22" s="23" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="20" t="s">
+      <c r="B23" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="20" t="s">
+      <c r="D23" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="23" t="s">
+      <c r="F23" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="23" t="s">
+      <c r="H23" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="L23" s="22" t="s">
+      <c r="L23" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="25" t="s">
+      <c r="M23" s="23" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="20" t="s">
+      <c r="B24" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="20" t="s">
+      <c r="D24" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G24" s="23" t="s">
+      <c r="F24" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" s="23" t="s">
+      <c r="H24" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J24" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K24" s="23" t="s">
+      <c r="J24" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L24" s="22" t="s">
+      <c r="L24" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M24" s="25" t="s">
+      <c r="M24" s="23" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="20" t="s">
+    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="20" t="s">
+      <c r="D25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="23" t="s">
+      <c r="F25" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H25" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="23" t="s">
+      <c r="H25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="J25" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K25" s="23" t="s">
+      <c r="K25" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="L25" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" s="25" t="s">
+      <c r="L25" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="23" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="20" t="s">
+      <c r="D26" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="23" t="s">
+      <c r="H26" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="J26" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="23" t="s">
+      <c r="J26" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L26" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M26" s="25" t="s">
+      <c r="L26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M26" s="23" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B27" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="B27" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="20" t="s">
+      <c r="D27" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="23" t="s">
+      <c r="F27" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" s="23" t="s">
+      <c r="H27" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J27" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K27" s="23" t="s">
+      <c r="J27" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M27" s="25" t="s">
+      <c r="L27" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M27" s="23" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
+    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="23" t="s">
+      <c r="F28" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I28" s="23" t="s">
+      <c r="I28" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="23" t="s">
+      <c r="J28" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L28" s="22" t="s">
+      <c r="L28" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M28" s="25" t="s">
+      <c r="M28" s="23" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="D29" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I29" s="23" t="s">
+      <c r="H29" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="22" t="s">
+      <c r="J29" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="K29" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="22" t="s">
+      <c r="L29" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M29" s="25" t="s">
+      <c r="M29" s="23" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="s">
+    <row r="30" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C30" s="20" t="s">
+      <c r="B30" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="20" t="s">
+      <c r="D30" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="23" t="s">
+      <c r="F30" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I30" s="23" t="s">
+      <c r="I30" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="22" t="s">
+      <c r="J30" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="K30" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L30" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M30" s="25" t="s">
+      <c r="L30" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M30" s="23" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+    <row r="31" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="20" t="s">
+      <c r="B31" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="20" t="s">
+      <c r="D31" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="23" t="s">
+      <c r="F31" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H31" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I31" s="23" t="s">
+      <c r="H31" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J31" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K31" s="23" t="s">
+      <c r="J31" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="L31" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M31" s="25" t="s">
+      <c r="L31" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" s="23" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I32" s="23" t="s">
+      <c r="I32" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="J32" s="22" t="s">
+      <c r="J32" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="22" t="s">
+      <c r="L32" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M32" s="25" t="s">
+      <c r="M32" s="23" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="20" t="s">
+      <c r="B33" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="20" t="s">
+      <c r="D33" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" s="23" t="s">
+      <c r="F33" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G33" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="23" t="s">
+      <c r="I33" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J33" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K33" s="23" t="s">
+      <c r="J33" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L33" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M33" s="25" t="s">
+      <c r="L33" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="23" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
+    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="20" t="s">
+      <c r="B34" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" s="23" t="s">
+      <c r="H34" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J34" s="22" t="s">
+      <c r="J34" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K34" s="23" t="s">
+      <c r="K34" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="L34" s="22" t="s">
+      <c r="L34" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M34" s="25" t="s">
+      <c r="M34" s="23" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="20" t="s">
+      <c r="B35" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" s="23" t="s">
+      <c r="F35" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H35" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" s="23" t="s">
+      <c r="H35" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="J35" s="22" t="s">
+      <c r="J35" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="K35" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L35" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M35" s="25" t="s">
+      <c r="L35" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M35" s="23" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D36" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E36" s="20" t="s">
+      <c r="D36" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" s="23" t="s">
+      <c r="F36" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H36" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I36" s="23" t="s">
+      <c r="H36" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J36" s="22" t="s">
+      <c r="J36" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="K36" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L36" s="22" t="s">
+      <c r="L36" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M36" s="25" t="s">
+      <c r="M36" s="23" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="s">
+    <row r="37" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="20" t="s">
+      <c r="D37" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G37" s="23" t="s">
+      <c r="G37" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H37" s="22" t="s">
+      <c r="H37" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J37" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K37" s="23" t="s">
+      <c r="J37" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L37" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M37" s="25" t="s">
+      <c r="L37" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" s="23" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G38" s="23" t="s">
+      <c r="G38" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H38" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I38" s="23" t="s">
+      <c r="H38" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J38" s="22" t="s">
+      <c r="J38" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="K38" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="23" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="23" t="s">
+      <c r="F39" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H39" s="22" t="s">
+      <c r="H39" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="I39" s="23" t="s">
+      <c r="I39" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J39" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K39" s="23" t="s">
+      <c r="J39" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="L39" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M39" s="25" t="s">
+      <c r="L39" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M39" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
+      <c r="A40" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="20" t="s">
+      <c r="B40" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="F40" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G40" s="23" t="s">
+      <c r="F40" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H40" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I40" s="23" t="s">
+      <c r="H40" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="J40" s="22" t="s">
+      <c r="J40" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K40" s="23" t="s">
+      <c r="K40" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L40" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M40" s="25" t="s">
+      <c r="L40" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M40" s="23" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="20" t="s">
+      <c r="D41" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G41" s="23" t="s">
+      <c r="F41" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G41" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H41" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I41" s="23" t="s">
+      <c r="H41" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K41" s="23" t="s">
+      <c r="J41" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L41" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M41" s="25" t="s">
+      <c r="L41" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M41" s="23" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="20" t="s">
+    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="20" t="s">
+      <c r="B42" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="20" t="s">
+      <c r="D42" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F42" s="21" t="s">
+      <c r="F42" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="23" t="s">
+      <c r="G42" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H42" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I42" s="23" t="s">
+      <c r="H42" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I42" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J42" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K42" s="23" t="s">
+      <c r="J42" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K42" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L42" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M42" s="25" t="s">
+      <c r="L42" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M42" s="23" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H43" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I43" s="23" t="s">
+      <c r="H43" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J43" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K43" s="23" t="s">
+      <c r="J43" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L43" s="22" t="s">
+      <c r="L43" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M43" s="25" t="s">
+      <c r="M43" s="23" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G44" s="23" t="s">
+      <c r="F44" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J44" s="22" t="s">
+      <c r="J44" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="K44" s="23" t="s">
+      <c r="K44" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="L44" s="22" t="s">
+      <c r="L44" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="M44" s="25" t="s">
+      <c r="M44" s="23" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="20" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="20" t="s">
+      <c r="B45" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="20" t="s">
+      <c r="D45" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="G45" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H45" s="22" t="s">
+      <c r="H45" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I45" s="23" t="s">
+      <c r="I45" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J45" s="22" t="s">
+      <c r="J45" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K45" s="23" t="s">
+      <c r="K45" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="L45" s="22" t="s">
+      <c r="L45" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="M45" s="25" t="s">
+      <c r="M45" s="23" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="20" t="s">
+      <c r="B46" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F46" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="23" t="s">
+      <c r="F46" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="H46" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="23" t="s">
+      <c r="H46" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="J46" s="22" t="s">
+      <c r="J46" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K46" s="23" t="s">
+      <c r="K46" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="L46" s="22" t="s">
+      <c r="L46" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M46" s="25" t="s">
+      <c r="M46" s="23" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="20" t="s">
+    <row r="47" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="20" t="s">
+      <c r="B47" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E47" s="20" t="s">
+      <c r="D47" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E47" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H47" s="22" t="s">
+      <c r="H47" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I47" s="23" t="s">
+      <c r="I47" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J47" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K47" s="23" t="s">
+      <c r="J47" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="L47" s="22" t="s">
+      <c r="L47" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="M47" s="25" t="s">
+      <c r="M47" s="23" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
+    <row r="48" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="20" t="s">
+      <c r="B48" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="20" t="s">
+      <c r="D48" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="G48" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="H48" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I48" s="23" t="s">
+      <c r="H48" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I48" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J48" s="22" t="s">
+      <c r="J48" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K48" s="23" t="s">
+      <c r="K48" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="L48" s="22" t="s">
+      <c r="L48" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="19" t="s">
+      <c r="M48" s="23" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="20" t="s">
+      <c r="B49" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G49" s="23" t="s">
+      <c r="G49" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="H49" s="22" t="s">
+      <c r="H49" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="J49" s="22" t="s">
+      <c r="J49" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K49" s="23" t="s">
+      <c r="K49" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="L49" s="22" t="s">
+      <c r="L49" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M49" s="19" t="s">
+      <c r="M49" s="23" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="20" t="s">
+      <c r="A50" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B50" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="20" t="s">
+      <c r="B50" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="20" t="s">
+      <c r="D50" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G50" s="23" t="s">
+      <c r="G50" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H50" s="22" t="s">
+      <c r="H50" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="23" t="s">
+      <c r="I50" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J50" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="23" t="s">
+      <c r="J50" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L50" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M50" s="25" t="s">
+      <c r="L50" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M50" s="23" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="20" t="s">
+      <c r="B51" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D51" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G51" s="23" t="s">
+      <c r="G51" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H51" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I51" s="23" t="s">
+      <c r="H51" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J51" s="22" t="s">
+      <c r="J51" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="23" t="s">
+      <c r="K51" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="L51" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M51" s="25" t="s">
+      <c r="L51" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" s="23" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
+    <row r="52" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C52" s="20" t="s">
+      <c r="B52" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F52" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" s="23" t="s">
+      <c r="F52" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H52" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I52" s="23" t="s">
+      <c r="H52" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I52" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J52" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K52" s="23" t="s">
+      <c r="J52" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K52" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="22" t="s">
+      <c r="L52" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M52" s="25" t="s">
+      <c r="M52" s="23" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="20" t="s">
+    <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="G53" s="23" t="s">
+      <c r="G53" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H53" s="22" t="s">
+      <c r="H53" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I53" s="23" t="s">
+      <c r="I53" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="J53" s="22" t="s">
+      <c r="J53" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K53" s="23" t="s">
+      <c r="K53" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="L53" s="22" t="s">
+      <c r="L53" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M53" s="19" t="s">
+      <c r="M53" s="23" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="20" t="s">
+    <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E54" s="20" t="s">
+      <c r="D54" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F54" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G54" s="23" t="s">
+      <c r="F54" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H54" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I54" s="23" t="s">
+      <c r="H54" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="J54" s="22" t="s">
+      <c r="J54" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K54" s="23" t="s">
+      <c r="K54" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L54" s="22" t="s">
+      <c r="L54" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M54" s="19" t="s">
+      <c r="M54" s="23" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="20" t="s">
+      <c r="B55" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="D55" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F55" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="23" t="s">
+      <c r="F55" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H55" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I55" s="23" t="s">
+      <c r="H55" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I55" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J55" s="22" t="s">
+      <c r="J55" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K55" s="23" t="s">
+      <c r="K55" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="L55" s="22" t="s">
+      <c r="L55" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="M55" s="25" t="s">
+      <c r="M55" s="23" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="20" t="s">
+      <c r="B56" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="D56" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F56" s="21" t="s">
+      <c r="F56" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G56" s="23" t="s">
+      <c r="G56" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H56" s="22" t="s">
+      <c r="H56" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I56" s="23" t="s">
+      <c r="I56" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J56" s="22" t="s">
+      <c r="J56" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K56" s="23" t="s">
+      <c r="K56" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="L56" s="22" t="s">
+      <c r="L56" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="M56" s="25" t="s">
+      <c r="M56" s="23" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
+    <row r="57" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="20" t="s">
+      <c r="B57" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" s="23" t="s">
+      <c r="F57" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H57" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I57" s="23" t="s">
+      <c r="H57" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I57" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J57" s="22" t="s">
+      <c r="J57" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K57" s="23" t="s">
+      <c r="K57" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="L57" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M57" s="25" t="s">
+      <c r="L57" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M57" s="23" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="20" t="s">
+    <row r="58" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D58" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="20" t="s">
+      <c r="D58" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F58" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G58" s="23" t="s">
+      <c r="F58" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G58" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="H58" s="22" t="s">
+      <c r="H58" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I58" s="23" t="s">
+      <c r="I58" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="J58" s="22" t="s">
+      <c r="J58" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K58" s="23" t="s">
+      <c r="K58" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L58" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M58" s="25" t="s">
+      <c r="L58" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M58" s="23" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B59" s="21" t="s">
+      <c r="B59" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C59" s="20" t="s">
+      <c r="C59" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="F59" s="21" t="s">
+      <c r="F59" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="G59" s="23" t="s">
+      <c r="G59" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="H59" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I59" s="23" t="s">
+      <c r="H59" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J59" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K59" s="23" t="s">
+      <c r="J59" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K59" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M59" s="19" t="s">
+      <c r="L59" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M59" s="23" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C60" s="20" t="s">
+      <c r="B60" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="21" t="s">
+      <c r="D60" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G60" s="23" t="s">
+      <c r="F60" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J60" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K60" s="23" t="s">
+      <c r="J60" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L60" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M60" s="19" t="s">
+      <c r="L60" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M60" s="23" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B61" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" s="20" t="s">
+      <c r="B61" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="D61" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="20" t="s">
+      <c r="D61" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="G61" s="23" t="s">
+      <c r="G61" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H61" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I61" s="23" t="s">
+      <c r="H61" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="J61" s="22" t="s">
+      <c r="J61" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K61" s="23" t="s">
+      <c r="K61" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L61" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M61" s="25" t="s">
+      <c r="L61" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M61" s="23" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="20" t="s">
+    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B62" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="20" t="s">
+      <c r="B62" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D62" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="20" t="s">
+      <c r="D62" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E62" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F62" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G62" s="23" t="s">
+      <c r="F62" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H62" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I62" s="23" t="s">
+      <c r="H62" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I62" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J62" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K62" s="23" t="s">
+      <c r="J62" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L62" s="22" t="s">
+      <c r="L62" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M62" s="25" t="s">
+      <c r="M62" s="23" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
+    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G63" s="23" t="s">
+      <c r="F63" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H63" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I63" s="23" t="s">
+      <c r="H63" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I63" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="J63" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K63" s="23" t="s">
+      <c r="J63" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L63" s="22" t="s">
+      <c r="L63" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M63" s="25" t="s">
+      <c r="M63" s="23" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="20" t="s">
+      <c r="C64" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D64" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="20" t="s">
+      <c r="D64" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F64" s="21" t="s">
+      <c r="F64" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="J64" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K64" s="23" t="s">
+      <c r="J64" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="L64" s="22" t="s">
+      <c r="L64" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M64" s="19" t="s">
+      <c r="M64" s="23" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="20" t="s">
+    <row r="65" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B65" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="20" t="s">
+      <c r="B65" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D65" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="20" t="s">
+      <c r="D65" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F65" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G65" s="23" t="s">
+      <c r="F65" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G65" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H65" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I65" s="23" t="s">
+      <c r="H65" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I65" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J65" s="22" t="s">
+      <c r="J65" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K65" s="23" t="s">
+      <c r="K65" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L65" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M65" s="25" t="s">
+      <c r="L65" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M65" s="23" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="20" t="s">
+    <row r="66" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="20" t="s">
+      <c r="C66" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D66" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="20" t="s">
+      <c r="D66" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F66" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G66" s="23" t="s">
+      <c r="F66" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G66" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H66" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I66" s="23" t="s">
+      <c r="H66" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J66" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K66" s="23" t="s">
+      <c r="J66" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K66" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="L66" s="22" t="s">
+      <c r="L66" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M66" s="25" t="s">
+      <c r="M66" s="23" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="20" t="s">
+    <row r="67" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B67" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" s="20" t="s">
+      <c r="B67" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D67" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="20" t="s">
+      <c r="D67" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F67" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="23" t="s">
+      <c r="F67" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G67" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H67" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I67" s="23" t="s">
+      <c r="H67" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="J67" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K67" s="23" t="s">
+      <c r="J67" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K67" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L67" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M67" s="19" t="s">
+      <c r="L67" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M67" s="23" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="20" t="s">
+    <row r="68" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B68" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="20" t="s">
+      <c r="B68" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D68" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E68" s="20" t="s">
+      <c r="D68" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="21" t="s">
+      <c r="F68" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H68" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I68" s="23" t="s">
+      <c r="H68" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I68" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J68" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K68" s="23" t="s">
+      <c r="J68" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L68" s="22" t="s">
+      <c r="L68" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M68" s="25" t="s">
+      <c r="M68" s="23" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="s">
+    <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="21" t="s">
+      <c r="B69" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C69" s="20" t="s">
+      <c r="C69" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F69" s="21" t="s">
+      <c r="F69" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G69" s="23" t="s">
+      <c r="G69" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H69" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I69" s="23" t="s">
+      <c r="H69" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I69" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="J69" s="22" t="s">
+      <c r="J69" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K69" s="23" t="s">
+      <c r="K69" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="L69" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M69" s="25" t="s">
+      <c r="L69" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M69" s="23" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B70" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="20" t="s">
+      <c r="B70" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D70" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="20" t="s">
+      <c r="D70" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="21" t="s">
+      <c r="F70" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G70" s="23" t="s">
+      <c r="G70" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="22" t="s">
+      <c r="H70" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="I70" s="23" t="s">
+      <c r="I70" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J70" s="22" t="s">
+      <c r="J70" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K70" s="23" t="s">
+      <c r="K70" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L70" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M70" s="25" t="s">
+      <c r="L70" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M70" s="23" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B71" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C71" s="20" t="s">
+      <c r="B71" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D71" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E71" s="20" t="s">
+      <c r="D71" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F71" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G71" s="23" t="s">
+      <c r="F71" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="H71" s="22" t="s">
+      <c r="H71" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="I71" s="23" t="s">
+      <c r="I71" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="J71" s="22" t="s">
+      <c r="J71" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K71" s="23" t="s">
+      <c r="K71" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="L71" s="22" t="s">
+      <c r="L71" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M71" s="25" t="s">
+      <c r="M71" s="23" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="20" t="s">
+    <row r="72" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D72" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="20" t="s">
+      <c r="D72" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G72" s="23" t="s">
+      <c r="G72" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H72" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I72" s="23" t="s">
+      <c r="I72" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="J72" s="22" t="s">
+      <c r="J72" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K72" s="23" t="s">
+      <c r="K72" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="L72" s="22" t="s">
+      <c r="L72" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M72" s="25" t="s">
+      <c r="M72" s="23" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="20" t="s">
+    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D73" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="20" t="s">
+      <c r="D73" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F73" s="21" t="s">
+      <c r="F73" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G73" s="23" t="s">
+      <c r="G73" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I73" s="23" t="s">
+      <c r="H73" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I73" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J73" s="22" t="s">
+      <c r="J73" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K73" s="23" t="s">
+      <c r="K73" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L73" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M73" s="25" t="s">
+      <c r="L73" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M73" s="23" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C74" s="20" t="s">
+      <c r="C74" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="20" t="s">
+      <c r="D74" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="F74" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G74" s="23" t="s">
+      <c r="G74" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H74" s="22" t="s">
+      <c r="H74" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I74" s="23" t="s">
+      <c r="I74" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J74" s="22" t="s">
+      <c r="J74" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K74" s="23" t="s">
+      <c r="K74" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L74" s="22" t="s">
+      <c r="L74" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="M74" s="25" t="s">
+      <c r="M74" s="23" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="20" t="s">
+    <row r="75" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B75" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" s="20" t="s">
+      <c r="B75" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E75" s="20" t="s">
+      <c r="E75" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="F75" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G75" s="23" t="s">
+      <c r="F75" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G75" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H75" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I75" s="23" t="s">
+      <c r="H75" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I75" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J75" s="22" t="s">
+      <c r="J75" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K75" s="23" t="s">
+      <c r="K75" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L75" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" s="19" t="s">
+      <c r="L75" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" s="23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A76" s="20" t="s">
+    <row r="76" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="20" t="s">
+      <c r="B76" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="F76" s="21" t="s">
+      <c r="F76" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="G76" s="23" t="s">
+      <c r="G76" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H76" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I76" s="23" t="s">
+      <c r="H76" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J76" s="22" t="s">
+      <c r="J76" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K76" s="23" t="s">
+      <c r="K76" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="L76" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" s="25" t="s">
+      <c r="L76" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" s="23" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="20" t="s">
+    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B77" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="20" t="s">
+      <c r="B77" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D77" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E77" s="20" t="s">
+      <c r="D77" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F77" s="21" t="s">
+      <c r="F77" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G77" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="H77" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I77" s="23" t="s">
+      <c r="I77" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="J77" s="22" t="s">
+      <c r="J77" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K77" s="23" t="s">
+      <c r="K77" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="L77" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M77" s="19" t="s">
+      <c r="L77" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M77" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A78" s="20" t="s">
+    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="20" t="s">
+      <c r="B78" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D78" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="20" t="s">
+      <c r="D78" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F78" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" s="23" t="s">
+      <c r="F78" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="H78" s="22" t="s">
+      <c r="H78" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I78" s="23" t="s">
+      <c r="I78" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J78" s="22" t="s">
+      <c r="J78" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K78" s="23" t="s">
+      <c r="K78" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L78" s="22" t="s">
+      <c r="L78" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M78" s="25" t="s">
+      <c r="M78" s="23" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="20" t="s">
+    <row r="79" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B79" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="20" t="s">
+      <c r="B79" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F79" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G79" s="23" t="s">
+      <c r="F79" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G79" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H79" s="22" t="s">
+      <c r="H79" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I79" s="23" t="s">
+      <c r="I79" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J79" s="22" t="s">
+      <c r="J79" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="K79" s="23" t="s">
+      <c r="K79" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="L79" s="22" t="s">
+      <c r="L79" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M79" s="25" t="s">
+      <c r="M79" s="23" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A80" s="20" t="s">
+    <row r="80" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B80" s="21" t="s">
+      <c r="B80" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F80" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G80" s="23" t="s">
+      <c r="F80" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G80" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I80" s="23" t="s">
+      <c r="I80" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="J80" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K80" s="23" t="s">
+      <c r="J80" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K80" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L80" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M80" s="19" t="s">
+      <c r="L80" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M80" s="23" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="81" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B81" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C81" s="20" t="s">
+      <c r="B81" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C81" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D81" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="20" t="s">
+      <c r="D81" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="F81" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G81" s="23" t="s">
+      <c r="F81" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G81" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H81" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I81" s="23" t="s">
+      <c r="H81" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I81" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J81" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K81" s="23" t="s">
+      <c r="J81" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K81" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L81" s="22" t="s">
+      <c r="L81" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="M81" s="25" t="s">
+      <c r="M81" s="23" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="20" t="s">
+    <row r="82" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B82" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C82" s="20" t="s">
+      <c r="B82" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D82" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="20" t="s">
+      <c r="D82" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F82" s="21" t="s">
+      <c r="F82" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G82" s="23" t="s">
+      <c r="G82" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H82" s="22" t="s">
+      <c r="H82" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I82" s="23" t="s">
+      <c r="I82" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="J82" s="22" t="s">
+      <c r="J82" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="K82" s="23" t="s">
+      <c r="K82" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="L82" s="22" t="s">
+      <c r="L82" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M82" s="25" t="s">
+      <c r="M82" s="23" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A83" s="20" t="s">
+      <c r="A83" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B83" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C83" s="20" t="s">
+      <c r="B83" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="E83" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F83" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G83" s="23" t="s">
+      <c r="F83" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H83" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I83" s="23" t="s">
+      <c r="H83" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J83" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K83" s="23" t="s">
+      <c r="J83" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K83" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="L83" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M83" s="25" t="s">
+      <c r="L83" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M83" s="23" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A84" s="20" t="s">
+    <row r="84" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A84" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="21" t="s">
+      <c r="B84" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C84" s="20" t="s">
+      <c r="C84" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E84" s="20" t="s">
+      <c r="E84" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F84" s="21" t="s">
+      <c r="F84" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="G84" s="23" t="s">
+      <c r="G84" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H84" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I84" s="23" t="s">
+      <c r="H84" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J84" s="22" t="s">
+      <c r="J84" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K84" s="23" t="s">
+      <c r="K84" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="L84" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M84" s="19" t="s">
+      <c r="L84" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M84" s="23" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A85" s="20" t="s">
+    <row r="85" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B85" s="21" t="s">
+      <c r="B85" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D85" s="21" t="s">
+      <c r="D85" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E85" s="20" t="s">
+      <c r="E85" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F85" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G85" s="23" t="s">
+      <c r="F85" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H85" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I85" s="23" t="s">
+      <c r="H85" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I85" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J85" s="22" t="s">
+      <c r="J85" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K85" s="23" t="s">
+      <c r="K85" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="L85" s="22" t="s">
+      <c r="L85" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M85" s="25" t="s">
+      <c r="M85" s="23" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="20" t="s">
+    <row r="86" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A86" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B86" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="20" t="s">
+      <c r="B86" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D86" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" s="20" t="s">
+      <c r="D86" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F86" s="21" t="s">
+      <c r="F86" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G86" s="23" t="s">
+      <c r="G86" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I86" s="23" t="s">
+      <c r="I86" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="J86" s="22" t="s">
+      <c r="J86" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K86" s="23" t="s">
+      <c r="K86" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="L86" s="22" t="s">
+      <c r="L86" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M86" s="25" t="s">
+      <c r="M86" s="23" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A87" s="20" t="s">
+      <c r="A87" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B87" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="20" t="s">
+      <c r="B87" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E87" s="20" t="s">
+      <c r="E87" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F87" s="21" t="s">
+      <c r="F87" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G87" s="23" t="s">
+      <c r="G87" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="H87" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I87" s="23" t="s">
+      <c r="H87" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I87" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J87" s="22" t="s">
+      <c r="J87" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K87" s="23" t="s">
+      <c r="K87" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="L87" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M87" s="19" t="s">
+      <c r="L87" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M87" s="23" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A88" s="20" t="s">
+      <c r="A88" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="B88" s="21" t="s">
+      <c r="B88" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D88" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E88" s="20" t="s">
+      <c r="D88" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E88" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F88" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G88" s="23" t="s">
+      <c r="F88" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H88" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I88" s="23" t="s">
+      <c r="H88" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J88" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K88" s="23" t="s">
+      <c r="J88" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K88" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L88" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M88" s="25" t="s">
+      <c r="L88" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M88" s="23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A89" s="20" t="s">
+    <row r="89" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A89" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B89" s="21" t="s">
+      <c r="B89" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E89" s="20" t="s">
+      <c r="E89" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F89" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G89" s="23" t="s">
+      <c r="F89" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G89" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="H89" s="22" t="s">
+      <c r="H89" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="I89" s="23" t="s">
+      <c r="I89" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="J89" s="22" t="s">
+      <c r="J89" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K89" s="23" t="s">
+      <c r="K89" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="L89" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M89" s="19" t="s">
+      <c r="L89" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M89" s="23" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A90" s="20" t="s">
+    <row r="90" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A90" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B90" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C90" s="20" t="s">
+      <c r="B90" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="21" t="s">
+      <c r="D90" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E90" s="20" t="s">
+      <c r="E90" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="F90" s="21" t="s">
+      <c r="F90" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G90" s="23" t="s">
+      <c r="G90" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H90" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I90" s="23" t="s">
+      <c r="H90" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="J90" s="22" t="s">
+      <c r="J90" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K90" s="23" t="s">
+      <c r="K90" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="L90" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M90" s="25" t="s">
+      <c r="L90" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M90" s="23" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A91" s="20" t="s">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A91" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B91" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="20" t="s">
+      <c r="B91" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E91" s="20" t="s">
+      <c r="E91" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F91" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G91" s="23" t="s">
+      <c r="F91" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G91" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H91" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I91" s="23" t="s">
+      <c r="H91" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I91" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="J91" s="22" t="s">
+      <c r="J91" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K91" s="23" t="s">
+      <c r="K91" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L91" s="22" t="s">
+      <c r="L91" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M91" s="19" t="s">
+      <c r="M91" s="23" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="20" t="s">
+    <row r="92" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A92" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B92" s="21" t="s">
+      <c r="B92" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C92" s="20" t="s">
+      <c r="C92" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E92" s="20" t="s">
+      <c r="E92" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F92" s="21" t="s">
+      <c r="F92" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G92" s="23" t="s">
+      <c r="G92" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H92" s="22" t="s">
+      <c r="H92" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I92" s="23" t="s">
+      <c r="I92" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J92" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K92" s="23" t="s">
+      <c r="J92" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K92" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L92" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M92" s="19" t="s">
+      <c r="L92" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M92" s="23" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B93" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C93" s="20" t="s">
+      <c r="B93" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E93" s="20" t="s">
+      <c r="E93" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F93" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G93" s="23" t="s">
+      <c r="F93" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G93" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="H93" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="I93" s="23" t="s">
+      <c r="H93" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J93" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="K93" s="23" t="s">
+      <c r="J93" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K93" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="L93" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M93" s="25" t="s">
+      <c r="L93" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M93" s="23" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A94" s="20" t="s">
+      <c r="A94" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B94" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C94" s="20" t="s">
+      <c r="B94" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C94" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E94" s="20" t="s">
+      <c r="E94" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F94" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G94" s="23" t="s">
+      <c r="F94" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G94" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="H94" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="I94" s="23" t="s">
+      <c r="I94" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J94" s="22" t="s">
+      <c r="J94" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K94" s="23" t="s">
+      <c r="K94" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L94" s="22" t="s">
+      <c r="L94" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="M94" s="19" t="s">
+      <c r="M94" s="23" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C95" s="20" t="s">
+      <c r="B95" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C95" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D95" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" s="20" t="s">
+      <c r="D95" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F95" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G95" s="23" t="s">
+      <c r="F95" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G95" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="H95" s="22" t="s">
+      <c r="H95" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I95" s="23" t="s">
+      <c r="I95" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="J95" s="22" t="s">
+      <c r="J95" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="K95" s="23" t="s">
+      <c r="K95" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="L95" s="22" t="s">
+      <c r="L95" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="M95" s="25" t="s">
+      <c r="M95" s="23" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A96" s="20" t="s">
+    <row r="96" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B96" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C96" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D96" s="21" t="s">
+      <c r="D96" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E96" s="20" t="s">
+      <c r="E96" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="F96" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G96" s="23" t="s">
+      <c r="F96" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G96" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H96" s="22" t="s">
+      <c r="H96" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I96" s="23" t="s">
+      <c r="I96" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="J96" s="22" t="s">
+      <c r="J96" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K96" s="23" t="s">
+      <c r="K96" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L96" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M96" s="19" t="s">
+      <c r="L96" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M96" s="23" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A97" s="20" t="s">
+    <row r="97" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A97" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C97" s="20" t="s">
+      <c r="B97" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="D97" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E97" s="20" t="s">
+      <c r="E97" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="F97" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G97" s="23" t="s">
+      <c r="F97" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G97" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="H97" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I97" s="23" t="s">
+      <c r="H97" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I97" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J97" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K97" s="23" t="s">
+      <c r="J97" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K97" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="L97" s="22" t="s">
+      <c r="L97" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="M97" s="25" t="s">
+      <c r="M97" s="23" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A98" s="20" t="s">
+    <row r="98" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A98" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B98" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C98" s="20" t="s">
+      <c r="B98" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D98" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98" s="20" t="s">
+      <c r="D98" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F98" s="21" t="s">
+      <c r="F98" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G98" s="23" t="s">
+      <c r="G98" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H98" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I98" s="23" t="s">
+      <c r="H98" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J98" s="22" t="s">
+      <c r="J98" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="K98" s="23" t="s">
+      <c r="K98" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L98" s="22" t="s">
+      <c r="L98" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M98" s="19" t="s">
+      <c r="M98" s="23" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A99" s="20" t="s">
+    <row r="99" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A99" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="B99" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C99" s="20" t="s">
+      <c r="B99" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C99" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D99" s="21" t="s">
+      <c r="D99" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="20" t="s">
+      <c r="E99" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F99" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G99" s="23" t="s">
+      <c r="F99" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G99" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="H99" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I99" s="23" t="s">
+      <c r="H99" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J99" s="22" t="s">
+      <c r="J99" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K99" s="23" t="s">
+      <c r="K99" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="L99" s="22" t="s">
+      <c r="L99" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M99" s="25" t="s">
+      <c r="M99" s="23" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A100" s="20" t="s">
+    <row r="100" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A100" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="B100" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C100" s="20" t="s">
+      <c r="B100" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="D100" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" s="20" t="s">
+      <c r="D100" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F100" s="21" t="s">
+      <c r="F100" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G100" s="23" t="s">
+      <c r="G100" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H100" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I100" s="23" t="s">
+      <c r="H100" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="J100" s="22" t="s">
+      <c r="J100" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K100" s="23" t="s">
+      <c r="K100" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="L100" s="22" t="s">
+      <c r="L100" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="M100" s="25" t="s">
+      <c r="M100" s="23" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A101" s="20" t="s">
+      <c r="A101" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B101" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C101" s="20" t="s">
+      <c r="B101" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D101" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E101" s="20" t="s">
+      <c r="D101" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="F101" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G101" s="23" t="s">
+      <c r="F101" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G101" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="H101" s="22" t="s">
+      <c r="H101" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I101" s="23" t="s">
+      <c r="I101" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="J101" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K101" s="23" t="s">
+      <c r="J101" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K101" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="L101" s="22" t="s">
+      <c r="L101" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="25" t="s">
+      <c r="M101" s="23" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A102" s="20" t="s">
+      <c r="A102" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B102" s="21" t="s">
+      <c r="B102" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="20" t="s">
+      <c r="C102" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D102" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="20" t="s">
+      <c r="D102" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E102" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F102" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G102" s="23" t="s">
+      <c r="F102" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="H102" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I102" s="23" t="s">
+      <c r="H102" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I102" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J102" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="K102" s="23" t="s">
+      <c r="J102" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K102" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L102" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="M102" s="25" t="s">
+      <c r="L102" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="M102" s="23" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A103" s="20" t="s">
+    <row r="103" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A103" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B103" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C103" s="20" t="s">
+      <c r="B103" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E103" s="20" t="s">
+      <c r="E103" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F103" s="21" t="s">
+      <c r="F103" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G103" s="23" t="s">
+      <c r="G103" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H103" s="22" t="s">
+      <c r="H103" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="I103" s="23" t="s">
+      <c r="I103" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="J103" s="22" t="s">
+      <c r="J103" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K103" s="23" t="s">
+      <c r="K103" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L103" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M103" s="25" t="s">
+      <c r="L103" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M103" s="23" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A104" s="20" t="s">
+    <row r="104" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="B104" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C104" s="20" t="s">
+      <c r="B104" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D104" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E104" s="20" t="s">
+      <c r="D104" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="F104" s="21" t="s">
+      <c r="F104" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G104" s="23" t="s">
+      <c r="G104" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H104" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I104" s="23" t="s">
+      <c r="H104" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I104" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J104" s="22" t="s">
+      <c r="J104" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K104" s="23" t="s">
+      <c r="K104" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="L104" s="22" t="s">
+      <c r="L104" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M104" s="25" t="s">
+      <c r="M104" s="23" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B105" s="21" t="s">
+      <c r="B105" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C105" s="20" t="s">
+      <c r="C105" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E105" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F105" s="21" t="s">
+      <c r="F105" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G105" s="23" t="s">
+      <c r="G105" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H105" s="22" t="s">
+      <c r="H105" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I105" s="23" t="s">
+      <c r="I105" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="J105" s="22" t="s">
+      <c r="J105" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K105" s="23" t="s">
+      <c r="K105" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="L105" s="22" t="s">
+      <c r="L105" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M105" s="25" t="s">
+      <c r="M105" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A106" s="20" t="s">
+    <row r="106" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A106" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B106" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C106" s="20" t="s">
+      <c r="B106" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D106" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E106" s="20" t="s">
+      <c r="D106" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F106" s="21" t="s">
+      <c r="F106" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G106" s="23" t="s">
+      <c r="G106" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="H106" s="22" t="s">
+      <c r="H106" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I106" s="23" t="s">
+      <c r="I106" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J106" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K106" s="23" t="s">
+      <c r="J106" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K106" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="L106" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="M106" s="25" t="s">
+      <c r="L106" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M106" s="23" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A107" s="20" t="s">
+    <row r="107" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A107" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B107" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C107" s="20" t="s">
+      <c r="B107" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D107" s="21" t="s">
+      <c r="D107" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E107" s="20" t="s">
+      <c r="E107" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F107" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G107" s="23" t="s">
+      <c r="F107" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G107" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="H107" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I107" s="23" t="s">
+      <c r="H107" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J107" s="22" t="s">
+      <c r="J107" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K107" s="23" t="s">
+      <c r="K107" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L107" s="22" t="s">
+      <c r="L107" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M107" s="25" t="s">
+      <c r="M107" s="23" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="20" t="s">
+    <row r="108" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A108" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B108" s="21" t="s">
+      <c r="B108" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D108" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E108" s="20" t="s">
+      <c r="D108" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F108" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G108" s="23" t="s">
+      <c r="F108" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="H108" s="22" t="s">
+      <c r="H108" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="I108" s="23" t="s">
+      <c r="I108" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J108" s="22" t="s">
+      <c r="J108" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="K108" s="23" t="s">
+      <c r="K108" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="L108" s="22" t="s">
+      <c r="L108" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="M108" s="25" t="s">
+      <c r="M108" s="23" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="20" t="s">
+    <row r="109" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A109" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="B109" s="21" t="s">
+      <c r="B109" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C109" s="20" t="s">
+      <c r="C109" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D109" s="21" t="s">
+      <c r="D109" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E109" s="20" t="s">
+      <c r="E109" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F109" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="G109" s="23" t="s">
+      <c r="F109" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G109" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="H109" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I109" s="23" t="s">
+      <c r="H109" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J109" s="22" t="s">
+      <c r="J109" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="K109" s="23" t="s">
+      <c r="K109" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="L109" s="22" t="s">
+      <c r="L109" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M109" s="25" t="s">
+      <c r="M109" s="23" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="110" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A110" s="20" t="s">
+      <c r="A110" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="B110" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C110" s="20" t="s">
+      <c r="B110" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C110" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D110" s="21" t="s">
+      <c r="D110" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E110" s="20" t="s">
+      <c r="E110" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F110" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G110" s="23" t="s">
+      <c r="F110" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G110" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="H110" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="I110" s="23" t="s">
+      <c r="H110" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I110" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="J110" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="K110" s="23" t="s">
+      <c r="J110" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K110" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="L110" s="22" t="s">
+      <c r="L110" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="M110" s="25" t="s">
+      <c r="M110" s="23" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A111" s="20" t="s">
+      <c r="A111" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B111" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C111" s="20" t="s">
+      <c r="B111" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="D111" s="21" t="s">
+      <c r="D111" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E111" s="20" t="s">
+      <c r="E111" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F111" s="21" t="s">
+      <c r="F111" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G111" s="23" t="s">
+      <c r="G111" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="H111" s="22" t="s">
+      <c r="H111" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="I111" s="23" t="s">
+      <c r="I111" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="J111" s="22" t="s">
+      <c r="J111" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="K111" s="23" t="s">
+      <c r="K111" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="L111" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="M111" s="25" t="s">
+      <c r="L111" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M111" s="23" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A112" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F112" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G112" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H112" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="J112" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K112" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="L112" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M112" s="23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A113" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B113" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F113" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H113" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I113" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="J113" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K113" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="L113" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M113" s="23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A114" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B114" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G114" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H114" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="I114" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="J114" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K114" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L114" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M114" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A115" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B115" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D115" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F115" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H115" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I115" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="J115" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K115" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="L115" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M115" s="23" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A116" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B116" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G116" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H116" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I116" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="J116" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="K116" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="L116" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="M116" s="23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A117" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B117" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D117" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F117" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="H117" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I117" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="J117" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K117" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="L117" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="M117" s="23" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A118" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D118" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F118" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G118" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H118" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J118" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K118" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L118" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M118" s="23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A119" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B119" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F119" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H119" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="J119" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K119" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="L119" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="M119" s="23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A120" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B120" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D120" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="G120" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H120" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I120" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="J120" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K120" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="L120" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="M120" s="23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A121" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B121" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F121" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G121" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H121" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="J121" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="K121" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="L121" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="M121" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B122" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C122" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F122" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G122" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I122" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J122" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="K122" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="L122" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="M122" s="23" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -8349,13 +8827,13 @@
           <x14:formula1>
             <xm:f>Information!$A$1:$A$80</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C111 A2:A111 G2:G111 K2:K111 E2:E111 I2:I111</xm:sqref>
+          <xm:sqref>A2:A122 G2:G122 K2:K122 E2:E122 I2:I122 C2:C122</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9E62CDE2-36BB-41FB-BCF8-DB5FFAD0C581}">
           <x14:formula1>
             <xm:f>Information!$D$1:$D$25</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B111 F2:F111 H2:H111 L2:L111 J2:J111 D2:D111</xm:sqref>
+          <xm:sqref>F2:F122 H2:H122 L2:L122 J2:J122 D2:D122 B2:B122</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
